--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC3FE87-81C3-4206-B704-97BB55D48CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AA1038-A507-4227-B1AA-D0754A9E12B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="3660" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="96">
   <si>
     <t>Total</t>
   </si>
@@ -366,6 +366,12 @@
   <si>
     <t>Sick (vomiting on way home from doc appt)</t>
   </si>
+  <si>
+    <t>10/??/2026</t>
+  </si>
+  <si>
+    <t>Not sick / Sparky undercoating, Ren maintenance</t>
+  </si>
 </sst>
 </file>
 
@@ -1490,7 +1496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="374">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2550,6 +2556,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3167,13 +3191,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178175</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4302,7 +4326,7 @@
       </c>
       <c r="C3" s="3">
         <f ca="1">160+C4</f>
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
@@ -4310,7 +4334,7 @@
       </c>
       <c r="E3" s="1">
         <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
@@ -4323,7 +4347,7 @@
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">IF((RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) &lt;&gt; "Template", (INDIRECT("'" &amp; (RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) - 1 &amp; "'!E3")) + (INDIRECT("'" &amp; (RIGHT(CELL("filename", A3), LEN(CELL("filename", A3)) - SEARCH("]", CELL("filename",A3)))) - 1 &amp; "'!E6")), 0)</f>
-        <v>28.000000000000004</v>
+        <v>20.000000000000007</v>
       </c>
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
@@ -4334,7 +4358,7 @@
       </c>
       <c r="C5" s="7">
         <f ca="1">C3/8</f>
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
@@ -4342,7 +4366,7 @@
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4747,7 +4771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:P48"/>
+  <dimension ref="B1:P49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4796,7 +4820,7 @@
         <v>168.5</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H47, "PTO", G14:G47)</f>
+        <f ca="1">C3 - C6 - SUMIF(H14:H48, "PTO", G14:G48)</f>
         <v>0</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
@@ -4841,11 +4865,11 @@
       </c>
       <c r="D6" s="10">
         <f>C6-E6</f>
-        <v>11.999999999999996</v>
+        <v>19.999999999999993</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H47, "Sick", G14:G47)</f>
-        <v>28.000000000000004</v>
+        <f>C6 - SUMIF(H14:H48, "Sick", G14:G48)</f>
+        <v>20.000000000000007</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1">
@@ -4858,11 +4882,11 @@
       </c>
       <c r="D7" s="13">
         <f>D6/8</f>
-        <v>1.4999999999999996</v>
+        <v>2.4999999999999991</v>
       </c>
       <c r="E7" s="14">
         <f>E6/8</f>
-        <v>3.5000000000000004</v>
+        <v>2.5000000000000009</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -4877,7 +4901,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H47, "Be You", G14:G47)</f>
+        <f>C8 - SUMIF(H14:H48, "Be You", G14:G48)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -4911,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H47, "Volunteer", G14:G47)</f>
+        <f>C10 - SUMIF(H14:H48, "Volunteer", G14:G48)</f>
         <v>4</v>
       </c>
       <c r="K10" s="36"/>
@@ -5443,7 +5467,7 @@
         <v>46234</v>
       </c>
       <c r="C26" s="331" t="str">
-        <f t="shared" ref="C26:C45" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
+        <f t="shared" ref="C26:C46" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D26" s="332">
@@ -5453,11 +5477,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="333">
-        <f t="shared" ref="F26:F42" si="6">((E26 - D26) * 24)</f>
+        <f t="shared" ref="F26:F43" si="6">((E26 - D26) * 24)</f>
         <v>5</v>
       </c>
       <c r="G26" s="331">
-        <f t="shared" ref="G26:G45" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
+        <f t="shared" ref="G26:G46" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
         <v>4</v>
       </c>
       <c r="H26" s="334" t="s">
@@ -5473,7 +5497,7 @@
         <v>59</v>
       </c>
       <c r="L26" s="336" t="str">
-        <f t="shared" ref="L26:L45" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L26:L46" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
@@ -5978,11 +6002,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F39" s="319">
-        <f t="shared" ref="F39" si="14">((E39 - D39) * 24)</f>
+        <f t="shared" ref="F39:F40" si="14">((E39 - D39) * 24)</f>
         <v>3.9999999999999991</v>
       </c>
       <c r="G39" s="317">
-        <f t="shared" ref="G39" si="15">IF(F39 &gt; 4, (F39 - 1), F39)</f>
+        <f t="shared" ref="G39:G40" si="15">IF(F39 &gt; 4, (F39 - 1), F39)</f>
         <v>3.9999999999999991</v>
       </c>
       <c r="H39" s="320" t="s">
@@ -6006,160 +6030,147 @@
       <c r="P39" s="353"/>
     </row>
     <row r="40" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B40" s="124">
+      <c r="B40" s="368" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="369"/>
+      <c r="D40" s="370">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E40" s="370">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F40" s="371">
+        <f t="shared" si="14"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G40" s="369">
+        <f t="shared" si="15"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H40" s="372" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="201" t="s">
+        <v>28</v>
+      </c>
+      <c r="J40" s="201" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40" s="373" t="s">
+        <v>95</v>
+      </c>
+      <c r="L40" s="194"/>
+      <c r="N40" s="351"/>
+      <c r="O40" s="352"/>
+      <c r="P40" s="353"/>
+    </row>
+    <row r="41" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B41" s="124">
         <v>46353</v>
       </c>
-      <c r="C40" s="173" t="str">
+      <c r="C41" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D40" s="155">
+      <c r="D41" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E40" s="155">
+      <c r="E41" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F40" s="226">
+      <c r="F41" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G40" s="173">
+      <c r="G41" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H40" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="269" t="s">
+      <c r="H41" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="L40" s="192" t="str">
+      <c r="L41" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N40" s="351" t="s">
+      <c r="N41" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="O40" s="352">
+      <c r="O41" s="352">
         <f>O38+1</f>
         <v>2025</v>
       </c>
-      <c r="P40" s="353">
+      <c r="P41" s="353">
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="2:16">
-      <c r="B41" s="112">
+    <row r="42" spans="2:16">
+      <c r="B42" s="112">
         <v>46380</v>
       </c>
-      <c r="C41" s="264" t="str">
+      <c r="C42" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D41" s="262">
+      <c r="D42" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E41" s="262">
+      <c r="E42" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F41" s="263">
+      <c r="F42" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G41" s="264">
+      <c r="G42" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H41" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="266" t="s">
+      <c r="H42" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="L41" s="42" t="str">
+      <c r="L42" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N41" s="343" t="s">
+      <c r="N42" s="343" t="s">
         <v>78</v>
       </c>
-      <c r="O41" s="70">
-        <f>O40+1</f>
+      <c r="O42" s="70">
+        <f>O41+1</f>
         <v>2026</v>
       </c>
-      <c r="P41" s="344">
+      <c r="P42" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="2:16">
-      <c r="B42" s="120">
+    <row r="43" spans="2:16">
+      <c r="B43" s="120">
         <v>46384</v>
       </c>
-      <c r="C42" s="274" t="str">
+      <c r="C43" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D42" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E42" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F42" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G42" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H42" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="L42" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="N42" s="343" t="s">
-        <v>79</v>
-      </c>
-      <c r="O42" s="70">
-        <f t="shared" ref="O42:O48" si="17">O41+1</f>
-        <v>2027</v>
-      </c>
-      <c r="P42" s="344">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16">
-      <c r="B43" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C43" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
       <c r="D43" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -6167,47 +6178,47 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F43" s="276">
-        <f t="shared" ref="F43:F45" si="18">((E43 - D43) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G43" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H43" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="273" t="s">
+      <c r="H43" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="L43" s="193" t="str">
+      <c r="L43" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
       <c r="N43" s="343" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O43" s="70">
-        <f t="shared" si="17"/>
-        <v>2028</v>
+        <f t="shared" ref="O43:O49" si="17">O42+1</f>
+        <v>2027</v>
       </c>
       <c r="P43" s="344">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="2:16">
       <c r="B44" s="270">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C44" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D44" s="275">
         <v>0.29166666666666669</v>
@@ -6216,7 +6227,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F44" s="276">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F44:F46" si="18">((E44 - D44) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G44" s="274">
@@ -6240,23 +6251,23 @@
         <v>Upcoming</v>
       </c>
       <c r="N44" s="343" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O44" s="70">
         <f t="shared" si="17"/>
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="P44" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B45" s="113">
-        <v>46387</v>
+    <row r="45" spans="2:16">
+      <c r="B45" s="270">
+        <v>46386</v>
       </c>
       <c r="C45" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D45" s="275">
         <v>0.29166666666666669</v>
@@ -6272,16 +6283,16 @@
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H45" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J45" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="268" t="s">
+      <c r="H45" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="273" t="s">
         <v>60</v>
       </c>
       <c r="L45" s="193" t="str">
@@ -6289,135 +6300,184 @@
         <v>Upcoming</v>
       </c>
       <c r="N45" s="343" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O45" s="70">
         <f t="shared" si="17"/>
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="P45" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="2:16">
-      <c r="B46" s="102"/>
-      <c r="C46" s="165" t="str">
-        <f t="shared" ref="C46:C47" si="19">IF(ISNUMBER(FIND("?", B46, 1)), "TBD", TEXT(B46, "ddd"))</f>
-        <v>Sat</v>
-      </c>
-      <c r="D46" s="157"/>
-      <c r="E46" s="157"/>
-      <c r="F46" s="220">
-        <f t="shared" ref="F46:F47" si="20">((E46 - D46) * 24)</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="217">
-        <f t="shared" ref="G46:G47" si="21">IF(F46 &gt; 4, (F46 - 1), F46)</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="180"/>
-      <c r="I46" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="J46" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="K46" s="205"/>
-      <c r="L46" s="252" t="str">
-        <f t="shared" ref="L46:L47" ca="1" si="22">IF(C46 = "TBD", "TBD", IF(B46 = "", "IDK!!", IF(TODAY() &gt; B46, "Passed", IF(TODAY() = B46, "Today!!", "Upcoming"))))</f>
-        <v>IDK!!</v>
+    <row r="46" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B46" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C46" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D46" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E46" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F46" s="276">
+        <f t="shared" si="18"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G46" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H46" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L46" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
       </c>
       <c r="N46" s="343" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O46" s="70">
         <f t="shared" si="17"/>
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="P46" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="47" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B47" s="259"/>
-      <c r="C47" s="253" t="str">
+    <row r="47" spans="2:16">
+      <c r="B47" s="102"/>
+      <c r="C47" s="165" t="str">
+        <f t="shared" ref="C47:C48" si="19">IF(ISNUMBER(FIND("?", B47, 1)), "TBD", TEXT(B47, "ddd"))</f>
+        <v>Sat</v>
+      </c>
+      <c r="D47" s="157"/>
+      <c r="E47" s="157"/>
+      <c r="F47" s="220">
+        <f t="shared" ref="F47:F48" si="20">((E47 - D47) * 24)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="217">
+        <f t="shared" ref="G47:G48" si="21">IF(F47 &gt; 4, (F47 - 1), F47)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="180"/>
+      <c r="I47" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="J47" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="K47" s="205"/>
+      <c r="L47" s="252" t="str">
+        <f t="shared" ref="L47:L48" ca="1" si="22">IF(C47 = "TBD", "TBD", IF(B47 = "", "IDK!!", IF(TODAY() &gt; B47, "Passed", IF(TODAY() = B47, "Today!!", "Upcoming"))))</f>
+        <v>IDK!!</v>
+      </c>
+      <c r="N47" s="343" t="s">
+        <v>83</v>
+      </c>
+      <c r="O47" s="70">
+        <f t="shared" si="17"/>
+        <v>2031</v>
+      </c>
+      <c r="P47" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B48" s="259"/>
+      <c r="C48" s="253" t="str">
         <f t="shared" si="19"/>
         <v>Sat</v>
       </c>
-      <c r="D47" s="260"/>
-      <c r="E47" s="260"/>
-      <c r="F47" s="261">
+      <c r="D48" s="260"/>
+      <c r="E48" s="260"/>
+      <c r="F48" s="261">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="G47" s="253">
+      <c r="G48" s="253">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H47" s="254"/>
-      <c r="I47" s="202" t="s">
+      <c r="H48" s="254"/>
+      <c r="I48" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J47" s="202" t="s">
+      <c r="J48" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="K47" s="255"/>
-      <c r="L47" s="251" t="str">
+      <c r="K48" s="255"/>
+      <c r="L48" s="251" t="str">
         <f t="shared" ca="1" si="22"/>
         <v>IDK!!</v>
       </c>
-      <c r="N47" s="343" t="s">
+      <c r="N48" s="343" t="s">
         <v>84</v>
       </c>
-      <c r="O47" s="70">
+      <c r="O48" s="70">
         <f t="shared" si="17"/>
         <v>2032</v>
       </c>
-      <c r="P47" s="344">
+      <c r="P48" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B48" s="86" t="s">
+    <row r="49" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B49" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="303"/>
-      <c r="D48" s="304"/>
-      <c r="E48" s="305"/>
-      <c r="F48" s="228">
-        <f>SUM(F14:F47)</f>
-        <v>179.5</v>
-      </c>
-      <c r="G48" s="256">
-        <f>SUM(G14:G47)</f>
-        <v>156.5</v>
-      </c>
-      <c r="H48" s="301"/>
-      <c r="I48" s="302"/>
-      <c r="J48" s="302"/>
-      <c r="K48" s="302"/>
-      <c r="L48" s="302"/>
-      <c r="N48" s="345" t="s">
+      <c r="C49" s="303"/>
+      <c r="D49" s="304"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="228">
+        <f>SUM(F14:F48)</f>
+        <v>188.5</v>
+      </c>
+      <c r="G49" s="256">
+        <f>SUM(G14:G48)</f>
+        <v>164.5</v>
+      </c>
+      <c r="H49" s="301"/>
+      <c r="I49" s="302"/>
+      <c r="J49" s="302"/>
+      <c r="K49" s="302"/>
+      <c r="L49" s="302"/>
+      <c r="N49" s="345" t="s">
         <v>85</v>
       </c>
-      <c r="O48" s="346">
+      <c r="O49" s="346">
         <f t="shared" si="17"/>
         <v>2033</v>
       </c>
-      <c r="P48" s="347">
+      <c r="P49" s="347">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B13:K48" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K49" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:L47">
+  <conditionalFormatting sqref="B14:L48">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F47 L14:L47">
+  <conditionalFormatting sqref="C14:F48 L14:L48">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -6432,7 +6492,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J47">
+  <conditionalFormatting sqref="I14:J48">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AA1038-A507-4227-B1AA-D0754A9E12B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD2631E-8BE9-4919-BB9C-5254004147A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="4380" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="95">
   <si>
     <t>Total</t>
   </si>
@@ -367,9 +367,6 @@
     <t>Sick (vomiting on way home from doc appt)</t>
   </si>
   <si>
-    <t>10/??/2026</t>
-  </si>
-  <si>
     <t>Not sick / Sparky undercoating, Ren maintenance</t>
   </si>
 </sst>
@@ -1496,7 +1493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="374">
+  <cellXfs count="375">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2557,22 +2554,25 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3191,13 +3191,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178175</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C3" s="3">
         <f ca="1">160+C4</f>
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="E3" s="1">
         <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">IF((RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) &lt;&gt; "Template", (INDIRECT("'" &amp; (RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) - 1 &amp; "'!E3")) + (INDIRECT("'" &amp; (RIGHT(CELL("filename", A3), LEN(CELL("filename", A3)) - SEARCH("]", CELL("filename",A3)))) - 1 &amp; "'!E6")), 0)</f>
-        <v>20.000000000000007</v>
+        <v>24.000000000000007</v>
       </c>
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="C5" s="7">
         <f ca="1">C3/8</f>
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4771,7 +4771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:P49"/>
+  <dimension ref="B1:P50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4820,7 +4820,7 @@
         <v>168.5</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H48, "PTO", G14:G48)</f>
+        <f ca="1">C3 - C6 - SUMIF(H14:H49, "PTO", G14:G49)</f>
         <v>0</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
@@ -4865,11 +4865,11 @@
       </c>
       <c r="D6" s="10">
         <f>C6-E6</f>
-        <v>19.999999999999993</v>
+        <v>15.999999999999993</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H48, "Sick", G14:G48)</f>
-        <v>20.000000000000007</v>
+        <f>C6 - SUMIF(H14:H49, "Sick", G14:G49)</f>
+        <v>24.000000000000007</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1">
@@ -4882,11 +4882,11 @@
       </c>
       <c r="D7" s="13">
         <f>D6/8</f>
-        <v>2.4999999999999991</v>
+        <v>1.9999999999999991</v>
       </c>
       <c r="E7" s="14">
         <f>E6/8</f>
-        <v>2.5000000000000009</v>
+        <v>3.0000000000000009</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -4901,7 +4901,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H48, "Be You", G14:G48)</f>
+        <f>C8 - SUMIF(H14:H49, "Be You", G14:G49)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
@@ -4935,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H48, "Volunteer", G14:G48)</f>
+        <f>C10 - SUMIF(H14:H49, "Volunteer", G14:G49)</f>
         <v>4</v>
       </c>
       <c r="K10" s="36"/>
@@ -5467,7 +5467,7 @@
         <v>46234</v>
       </c>
       <c r="C26" s="331" t="str">
-        <f t="shared" ref="C26:C46" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
+        <f t="shared" ref="C26:C47" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
         <v>Fri</v>
       </c>
       <c r="D26" s="332">
@@ -5477,11 +5477,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="333">
-        <f t="shared" ref="F26:F43" si="6">((E26 - D26) * 24)</f>
+        <f t="shared" ref="F26:F44" si="6">((E26 - D26) * 24)</f>
         <v>5</v>
       </c>
       <c r="G26" s="331">
-        <f t="shared" ref="G26:G46" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
+        <f t="shared" ref="G26:G47" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
         <v>4</v>
       </c>
       <c r="H26" s="334" t="s">
@@ -5497,7 +5497,7 @@
         <v>59</v>
       </c>
       <c r="L26" s="336" t="str">
-        <f t="shared" ref="L26:L46" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L26:L47" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
     </row>
@@ -6002,11 +6002,11 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F39" s="319">
-        <f t="shared" ref="F39:F40" si="14">((E39 - D39) * 24)</f>
+        <f t="shared" ref="F39:F41" si="14">((E39 - D39) * 24)</f>
         <v>3.9999999999999991</v>
       </c>
       <c r="G39" s="317">
-        <f t="shared" ref="G39:G40" si="15">IF(F39 &gt; 4, (F39 - 1), F39)</f>
+        <f t="shared" ref="G39:G41" si="15">IF(F39 &gt; 4, (F39 - 1), F39)</f>
         <v>3.9999999999999991</v>
       </c>
       <c r="H39" s="320" t="s">
@@ -6022,204 +6022,203 @@
         <v>93</v>
       </c>
       <c r="L39" s="60" t="str">
-        <f t="shared" ref="L39" ca="1" si="16">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L39:L41" ca="1" si="16">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
       <c r="N39" s="351"/>
       <c r="O39" s="352"/>
       <c r="P39" s="353"/>
     </row>
-    <row r="40" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B40" s="368" t="s">
+    <row r="40" spans="2:16">
+      <c r="B40" s="295">
+        <v>46297</v>
+      </c>
+      <c r="C40" s="296" t="str">
+        <f>IF(ISNUMBER(FIND("?", B40, 1)), "TBD", TEXT(B40, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D40" s="297">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E40" s="297">
+        <v>0.375</v>
+      </c>
+      <c r="F40" s="298">
+        <f t="shared" si="14"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="G40" s="296">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="H40" s="299" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="J40" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40" s="368" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="369"/>
-      <c r="D40" s="370">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E40" s="370">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F40" s="371">
-        <f t="shared" si="14"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G40" s="369">
-        <f t="shared" si="15"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H40" s="372" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="201" t="s">
-        <v>28</v>
-      </c>
-      <c r="J40" s="201" t="s">
-        <v>28</v>
-      </c>
-      <c r="K40" s="373" t="s">
-        <v>95</v>
-      </c>
-      <c r="L40" s="194"/>
+      <c r="L40" s="42" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v>Upcoming</v>
+      </c>
       <c r="N40" s="351"/>
       <c r="O40" s="352"/>
       <c r="P40" s="353"/>
     </row>
     <row r="41" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B41" s="124">
+      <c r="B41" s="369">
+        <v>46297</v>
+      </c>
+      <c r="C41" s="370" t="str">
+        <f>IF(ISNUMBER(FIND("?", B41, 1)), "TBD", TEXT(B41, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D41" s="371">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E41" s="371">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="372">
+        <f t="shared" si="14"/>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="G41" s="370">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="H41" s="373" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="K41" s="374" t="s">
+        <v>94</v>
+      </c>
+      <c r="L41" s="60" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="N41" s="351"/>
+      <c r="O41" s="352"/>
+      <c r="P41" s="353"/>
+    </row>
+    <row r="42" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B42" s="124">
         <v>46353</v>
       </c>
-      <c r="C41" s="173" t="str">
+      <c r="C42" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D41" s="155">
+      <c r="D42" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E41" s="155">
+      <c r="E42" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F41" s="226">
+      <c r="F42" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G41" s="173">
+      <c r="G42" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H41" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="269" t="s">
+      <c r="H42" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="L41" s="192" t="str">
+      <c r="L42" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N41" s="351" t="s">
+      <c r="N42" s="351" t="s">
         <v>77</v>
       </c>
-      <c r="O41" s="352">
+      <c r="O42" s="352">
         <f>O38+1</f>
         <v>2025</v>
       </c>
-      <c r="P41" s="353">
+      <c r="P42" s="353">
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="2:16">
-      <c r="B42" s="112">
+    <row r="43" spans="2:16">
+      <c r="B43" s="112">
         <v>46380</v>
       </c>
-      <c r="C42" s="264" t="str">
+      <c r="C43" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D42" s="262">
+      <c r="D43" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E42" s="262">
+      <c r="E43" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F42" s="263">
+      <c r="F43" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G42" s="264">
+      <c r="G43" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H42" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="266" t="s">
+      <c r="H43" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="L42" s="42" t="str">
+      <c r="L43" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N42" s="343" t="s">
+      <c r="N43" s="343" t="s">
         <v>78</v>
       </c>
-      <c r="O42" s="70">
-        <f>O41+1</f>
+      <c r="O43" s="70">
+        <f>O42+1</f>
         <v>2026</v>
       </c>
-      <c r="P42" s="344">
+      <c r="P43" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="2:16">
-      <c r="B43" s="120">
+    <row r="44" spans="2:16">
+      <c r="B44" s="120">
         <v>46384</v>
       </c>
-      <c r="C43" s="274" t="str">
+      <c r="C44" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D43" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E43" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F43" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G43" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H43" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="L43" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="N43" s="343" t="s">
-        <v>79</v>
-      </c>
-      <c r="O43" s="70">
-        <f t="shared" ref="O43:O49" si="17">O42+1</f>
-        <v>2027</v>
-      </c>
-      <c r="P43" s="344">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16">
-      <c r="B44" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C44" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
       <c r="D44" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -6227,47 +6226,47 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F44" s="276">
-        <f t="shared" ref="F44:F46" si="18">((E44 - D44) * 24)</f>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G44" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H44" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="273" t="s">
+      <c r="H44" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="L44" s="193" t="str">
+      <c r="L44" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
       <c r="N44" s="343" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O44" s="70">
-        <f t="shared" si="17"/>
-        <v>2028</v>
+        <f t="shared" ref="O44:O50" si="17">O43+1</f>
+        <v>2027</v>
       </c>
       <c r="P44" s="344">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="2:16">
       <c r="B45" s="270">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C45" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D45" s="275">
         <v>0.29166666666666669</v>
@@ -6276,7 +6275,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F45" s="276">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F45:F47" si="18">((E45 - D45) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G45" s="274">
@@ -6300,23 +6299,23 @@
         <v>Upcoming</v>
       </c>
       <c r="N45" s="343" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O45" s="70">
         <f t="shared" si="17"/>
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="P45" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B46" s="113">
-        <v>46387</v>
+    <row r="46" spans="2:16">
+      <c r="B46" s="270">
+        <v>46386</v>
       </c>
       <c r="C46" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Wed</v>
       </c>
       <c r="D46" s="275">
         <v>0.29166666666666669</v>
@@ -6332,16 +6331,16 @@
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H46" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="268" t="s">
+      <c r="H46" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="273" t="s">
         <v>60</v>
       </c>
       <c r="L46" s="193" t="str">
@@ -6349,135 +6348,184 @@
         <v>Upcoming</v>
       </c>
       <c r="N46" s="343" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O46" s="70">
         <f t="shared" si="17"/>
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="P46" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="47" spans="2:16">
-      <c r="B47" s="102"/>
-      <c r="C47" s="165" t="str">
-        <f t="shared" ref="C47:C48" si="19">IF(ISNUMBER(FIND("?", B47, 1)), "TBD", TEXT(B47, "ddd"))</f>
-        <v>Sat</v>
-      </c>
-      <c r="D47" s="157"/>
-      <c r="E47" s="157"/>
-      <c r="F47" s="220">
-        <f t="shared" ref="F47:F48" si="20">((E47 - D47) * 24)</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="217">
-        <f t="shared" ref="G47:G48" si="21">IF(F47 &gt; 4, (F47 - 1), F47)</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="180"/>
-      <c r="I47" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="J47" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="K47" s="205"/>
-      <c r="L47" s="252" t="str">
-        <f t="shared" ref="L47:L48" ca="1" si="22">IF(C47 = "TBD", "TBD", IF(B47 = "", "IDK!!", IF(TODAY() &gt; B47, "Passed", IF(TODAY() = B47, "Today!!", "Upcoming"))))</f>
-        <v>IDK!!</v>
+    <row r="47" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B47" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C47" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D47" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E47" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F47" s="276">
+        <f t="shared" si="18"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G47" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H47" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L47" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
       </c>
       <c r="N47" s="343" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O47" s="70">
         <f t="shared" si="17"/>
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="P47" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B48" s="259"/>
-      <c r="C48" s="253" t="str">
+    <row r="48" spans="2:16">
+      <c r="B48" s="102"/>
+      <c r="C48" s="165" t="str">
+        <f t="shared" ref="C48:C49" si="19">IF(ISNUMBER(FIND("?", B48, 1)), "TBD", TEXT(B48, "ddd"))</f>
+        <v>Sat</v>
+      </c>
+      <c r="D48" s="157"/>
+      <c r="E48" s="157"/>
+      <c r="F48" s="220">
+        <f t="shared" ref="F48:F49" si="20">((E48 - D48) * 24)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="217">
+        <f t="shared" ref="G48:G49" si="21">IF(F48 &gt; 4, (F48 - 1), F48)</f>
+        <v>0</v>
+      </c>
+      <c r="H48" s="180"/>
+      <c r="I48" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="J48" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="K48" s="205"/>
+      <c r="L48" s="252" t="str">
+        <f t="shared" ref="L48:L49" ca="1" si="22">IF(C48 = "TBD", "TBD", IF(B48 = "", "IDK!!", IF(TODAY() &gt; B48, "Passed", IF(TODAY() = B48, "Today!!", "Upcoming"))))</f>
+        <v>IDK!!</v>
+      </c>
+      <c r="N48" s="343" t="s">
+        <v>83</v>
+      </c>
+      <c r="O48" s="70">
+        <f t="shared" si="17"/>
+        <v>2031</v>
+      </c>
+      <c r="P48" s="344">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B49" s="259"/>
+      <c r="C49" s="253" t="str">
         <f t="shared" si="19"/>
         <v>Sat</v>
       </c>
-      <c r="D48" s="260"/>
-      <c r="E48" s="260"/>
-      <c r="F48" s="261">
+      <c r="D49" s="260"/>
+      <c r="E49" s="260"/>
+      <c r="F49" s="261">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="G48" s="253">
+      <c r="G49" s="253">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H48" s="254"/>
-      <c r="I48" s="202" t="s">
+      <c r="H49" s="254"/>
+      <c r="I49" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J48" s="202" t="s">
+      <c r="J49" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="K48" s="255"/>
-      <c r="L48" s="251" t="str">
+      <c r="K49" s="255"/>
+      <c r="L49" s="251" t="str">
         <f t="shared" ca="1" si="22"/>
         <v>IDK!!</v>
       </c>
-      <c r="N48" s="343" t="s">
+      <c r="N49" s="343" t="s">
         <v>84</v>
       </c>
-      <c r="O48" s="70">
+      <c r="O49" s="70">
         <f t="shared" si="17"/>
         <v>2032</v>
       </c>
-      <c r="P48" s="344">
+      <c r="P49" s="344">
         <v>176</v>
       </c>
     </row>
-    <row r="49" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B49" s="86" t="s">
+    <row r="50" spans="2:16" ht="15.75" thickBot="1">
+      <c r="B50" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="303"/>
-      <c r="D49" s="304"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="228">
-        <f>SUM(F14:F48)</f>
-        <v>188.5</v>
-      </c>
-      <c r="G49" s="256">
-        <f>SUM(G14:G48)</f>
-        <v>164.5</v>
-      </c>
-      <c r="H49" s="301"/>
-      <c r="I49" s="302"/>
-      <c r="J49" s="302"/>
-      <c r="K49" s="302"/>
-      <c r="L49" s="302"/>
-      <c r="N49" s="345" t="s">
+      <c r="C50" s="303"/>
+      <c r="D50" s="304"/>
+      <c r="E50" s="305"/>
+      <c r="F50" s="228">
+        <f>SUM(F14:F49)</f>
+        <v>183.5</v>
+      </c>
+      <c r="G50" s="256">
+        <f>SUM(G14:G49)</f>
+        <v>160.5</v>
+      </c>
+      <c r="H50" s="301"/>
+      <c r="I50" s="302"/>
+      <c r="J50" s="302"/>
+      <c r="K50" s="302"/>
+      <c r="L50" s="302"/>
+      <c r="N50" s="345" t="s">
         <v>85</v>
       </c>
-      <c r="O49" s="346">
+      <c r="O50" s="346">
         <f t="shared" si="17"/>
         <v>2033</v>
       </c>
-      <c r="P49" s="347">
+      <c r="P50" s="347">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B13:K49" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K50" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:L48">
+  <conditionalFormatting sqref="B14:L49">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F48 L14:L48">
+  <conditionalFormatting sqref="C14:F49 L14:L49">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -6492,7 +6540,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J48">
+  <conditionalFormatting sqref="I14:J49">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD2631E-8BE9-4919-BB9C-5254004147A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFEF643C-74C2-41CB-B233-513ED4E554ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="0" windowWidth="28800" windowHeight="20985" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="4380" yWindow="360" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -367,7 +367,7 @@
     <t>Sick (vomiting on way home from doc appt)</t>
   </si>
   <si>
-    <t>Not sick / Sparky undercoating, Ren maintenance</t>
+    <t>Not sick / Sparky undercoating</t>
   </si>
 </sst>
 </file>
@@ -6055,7 +6055,7 @@
         <v>32</v>
       </c>
       <c r="I40" s="196" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J40" s="196" t="s">
         <v>28</v>
@@ -6097,7 +6097,7 @@
         <v>32</v>
       </c>
       <c r="I41" s="244" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J41" s="244" t="s">
         <v>28</v>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\storage\I_Scratch\Git_Repository\PubRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFEF643C-74C2-41CB-B233-513ED4E554ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01938263-0121-4A4B-B71E-9D702133C310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="360" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="21615" yWindow="0" windowWidth="16830" windowHeight="13350" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$B$12:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$B$13:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2025_Original'!$B$13:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$13:$K$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2027'!$B$13:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Template!$B$13:$G$13</definedName>
   </definedNames>
@@ -33,30 +33,19 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -71,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="97">
   <si>
     <t>Total</t>
   </si>
@@ -369,6 +358,12 @@
   <si>
     <t>Not sick / Sparky undercoating</t>
   </si>
+  <si>
+    <t>G sick / helping get kids up, around &amp; dropped off</t>
+  </si>
+  <si>
+    <t>G sick / helping get kids picked up &amp; C to dentist</t>
+  </si>
 </sst>
 </file>
 
@@ -378,7 +373,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
     <numFmt numFmtId="165" formatCode="mm\/dd\/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1493,7 +1488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="375">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2405,24 +2400,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3191,13 +3168,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178175</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>5603</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3989,9 +3966,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4029,7 +4006,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4135,7 +4112,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4277,7 +4254,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4286,7 +4263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2671213-B148-403C-9F48-0EB30902282E}">
   <dimension ref="B1:W20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -4305,8 +4282,8 @@
     <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:12" ht="18" thickBot="1">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -4320,13 +4297,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:12">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3">
         <f ca="1">160+C4</f>
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
@@ -4334,31 +4311,31 @@
       </c>
       <c r="E3" s="1">
         <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
         <v>PTO Reset: 02/12/2028</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">IF((RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) &lt;&gt; "Template", (INDIRECT("'" &amp; (RIGHT(CELL("filename", A2), LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) - 1 &amp; "'!E3")) + (INDIRECT("'" &amp; (RIGHT(CELL("filename", A3), LEN(CELL("filename", A3)) - SEARCH("]", CELL("filename",A3)))) - 1 &amp; "'!E6")), 0)</f>
-        <v>24.000000000000007</v>
+        <v>20.000000000000007</v>
       </c>
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:12" ht="15.75" thickBot="1">
+    <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="7">
         <f ca="1">C3/8</f>
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="D5" s="7">
         <f ca="1">D3/8</f>
@@ -4366,10 +4343,10 @@
       </c>
       <c r="E5" s="8">
         <f ca="1">E3/8</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -4385,7 +4362,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.75" thickBot="1">
+    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -4402,7 +4379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -4419,7 +4396,7 @@
       </c>
       <c r="K8" s="51"/>
     </row>
-    <row r="9" spans="2:12" ht="15.75" thickBot="1">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -4436,7 +4413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -4453,7 +4430,7 @@
       </c>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="2:12" ht="15.75" thickBot="1">
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -4471,8 +4448,8 @@
       </c>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="2:12" ht="15.75" thickBot="1"/>
-    <row r="13" spans="2:12" ht="35.25" thickBot="1">
+    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -4507,7 +4484,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="122"/>
       <c r="C14" s="240" t="str">
         <f t="shared" ref="C14:C19" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
@@ -4536,7 +4513,7 @@
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15.75" thickBot="1">
+    <row r="15" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="306"/>
       <c r="C15" s="307" t="str">
         <f t="shared" si="0"/>
@@ -4565,35 +4542,35 @@
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="282">
         <v>46717</v>
       </c>
-      <c r="C16" s="355" t="str">
+      <c r="C16" s="349" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="D16" s="356">
+      <c r="D16" s="350">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E16" s="356">
+      <c r="E16" s="350">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F16" s="357">
+      <c r="F16" s="351">
         <f>((E16 - D16) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G16" s="355">
+      <c r="G16" s="349">
         <f>IF(F16 &gt; 4, (F16 - 1), F16)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H16" s="358" t="s">
+      <c r="H16" s="352" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="202" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="327" t="s">
+      <c r="J16" s="321" t="s">
         <v>28</v>
       </c>
       <c r="K16" s="288" t="s">
@@ -4604,7 +4581,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="17" spans="2:23" ht="15.75" thickBot="1">
+    <row r="17" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="104">
         <v>46720</v>
       </c>
@@ -4618,7 +4595,7 @@
       <c r="E17" s="313">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F17" s="357">
+      <c r="F17" s="351">
         <f>((E17 - D17) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
@@ -4635,7 +4612,7 @@
       <c r="J17" s="244" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="359" t="s">
+      <c r="K17" s="353" t="s">
         <v>89</v>
       </c>
       <c r="L17" s="60" t="str">
@@ -4643,7 +4620,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="18" spans="2:23" ht="15.75" thickBot="1">
+    <row r="18" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="102"/>
       <c r="C18" s="165" t="str">
         <f t="shared" si="0"/>
@@ -4671,19 +4648,19 @@
         <f t="shared" ca="1" si="2"/>
         <v>IDK!!</v>
       </c>
-      <c r="U18" s="345" t="s">
+      <c r="U18" s="339" t="s">
         <v>85</v>
       </c>
-      <c r="V18" s="346" t="e">
+      <c r="V18" s="340" t="e">
         <f>#REF!+1</f>
         <v>#REF!</v>
       </c>
-      <c r="W18" s="347">
+      <c r="W18" s="341">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
-    <row r="19" spans="2:23" ht="15.75" thickBot="1">
+    <row r="19" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="259"/>
       <c r="C19" s="253" t="str">
         <f t="shared" si="0"/>
@@ -4712,7 +4689,7 @@
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="20" spans="2:23" ht="15.75" thickBot="1">
+    <row r="20" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="86" t="s">
         <v>11</v>
       </c>
@@ -4771,8 +4748,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
-  <dimension ref="B1:P50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B1:P52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -4792,8 +4769,8 @@
     <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:12" ht="18" thickBot="1">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -4807,7 +4784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:12">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4820,7 +4797,7 @@
         <v>168.5</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H49, "PTO", G14:G49)</f>
+        <f ca="1">C3 - C6 - SUMIF(H14:H51, "PTO", G14:G51)</f>
         <v>0</v>
       </c>
       <c r="K3" s="56" t="str" cm="1">
@@ -4828,7 +4805,7 @@
         <v>PTO Reset: 02/12/2027</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -4839,7 +4816,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:12" ht="15.75" thickBot="1">
+    <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -4856,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -4865,14 +4842,14 @@
       </c>
       <c r="D6" s="10">
         <f>C6-E6</f>
-        <v>15.999999999999993</v>
+        <v>19.999999999999993</v>
       </c>
       <c r="E6" s="11">
-        <f>C6 - SUMIF(H14:H49, "Sick", G14:G49)</f>
-        <v>24.000000000000007</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="15.75" thickBot="1">
+        <f>C6 - SUMIF(H14:H51, "Sick", G14:G51)</f>
+        <v>20.000000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -4882,14 +4859,14 @@
       </c>
       <c r="D7" s="13">
         <f>D6/8</f>
-        <v>1.9999999999999991</v>
+        <v>2.4999999999999991</v>
       </c>
       <c r="E7" s="14">
         <f>E6/8</f>
-        <v>3.0000000000000009</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
+        <v>2.5000000000000009</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -4901,12 +4878,12 @@
         <v>16</v>
       </c>
       <c r="E8" s="1">
-        <f>C8 - SUMIF(H14:H49, "Be You", G14:G49)</f>
+        <f>C8 - SUMIF(H14:H51, "Be You", G14:G51)</f>
         <v>0</v>
       </c>
       <c r="K8" s="51"/>
     </row>
-    <row r="9" spans="2:12" ht="15.75" thickBot="1">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -4923,7 +4900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -4935,12 +4912,12 @@
         <v>0</v>
       </c>
       <c r="E10" s="129">
-        <f>C10 - SUMIF(H14:H49, "Volunteer", G14:G49)</f>
+        <f>C10 - SUMIF(H14:H51, "Volunteer", G14:G51)</f>
         <v>4</v>
       </c>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="2:12" ht="15.75" thickBot="1">
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -4958,8 +4935,8 @@
       </c>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="2:12" ht="15.75" thickBot="1"/>
-    <row r="13" spans="2:12" ht="35.25" thickBot="1">
+    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -4994,7 +4971,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="122">
         <v>46059</v>
       </c>
@@ -5033,7 +5010,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15.75" thickBot="1">
+    <row r="15" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="306">
         <v>46080</v>
       </c>
@@ -5072,7 +5049,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15.75" thickBot="1">
+    <row r="16" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="282">
         <v>46093</v>
       </c>
@@ -5100,7 +5077,7 @@
       <c r="I16" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="327" t="s">
+      <c r="J16" s="321" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="288" t="s">
@@ -5111,7 +5088,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="289">
         <v>46150</v>
       </c>
@@ -5150,7 +5127,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="270">
         <v>46164</v>
       </c>
@@ -5158,10 +5135,10 @@
         <f>IF(ISNUMBER(FIND("?", B18, 1)), "TBD", TEXT(B18, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D18" s="354">
+      <c r="D18" s="348">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E18" s="354">
+      <c r="E18" s="348">
         <v>0.66666666666666663</v>
       </c>
       <c r="F18" s="76">
@@ -5189,25 +5166,25 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15.75" thickBot="1">
+    <row r="19" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="113">
         <v>46168</v>
       </c>
-      <c r="C19" s="360" t="str">
+      <c r="C19" s="354" t="str">
         <f>IF(ISNUMBER(FIND("?", B19, 1)), "TBD", TEXT(B19, "ddd"))</f>
         <v>Tue</v>
       </c>
-      <c r="D19" s="361">
+      <c r="D19" s="355">
         <v>0.64583333333333337</v>
       </c>
-      <c r="E19" s="361">
+      <c r="E19" s="355">
         <v>0.66666666666666663</v>
       </c>
       <c r="F19" s="33">
         <f>((E19 - D19) * 24)</f>
         <v>0.49999999999999822</v>
       </c>
-      <c r="G19" s="360">
+      <c r="G19" s="354">
         <f>IF(F19 &gt; 4, (F19 - 1), F19)</f>
         <v>0.49999999999999822</v>
       </c>
@@ -5228,29 +5205,29 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="30.75" thickBot="1">
+    <row r="20" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="103">
         <v>46196</v>
       </c>
-      <c r="C20" s="362" t="str">
+      <c r="C20" s="356" t="str">
         <f>IF(ISNUMBER(FIND("?", B20, 1)), "TBD", TEXT(B20, "ddd"))</f>
         <v>Tue</v>
       </c>
-      <c r="D20" s="363">
+      <c r="D20" s="357">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E20" s="363">
+      <c r="E20" s="357">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F20" s="364">
+      <c r="F20" s="358">
         <f>((E20 - D20) * 24)</f>
         <v>3.9999999999999991</v>
       </c>
-      <c r="G20" s="362">
+      <c r="G20" s="356">
         <f>IF(F20 &gt; 4, (F20 - 1), F20)</f>
         <v>3.9999999999999991</v>
       </c>
-      <c r="H20" s="365" t="s">
+      <c r="H20" s="359" t="s">
         <v>4</v>
       </c>
       <c r="I20" s="196" t="s">
@@ -5259,7 +5236,7 @@
       <c r="J20" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="K20" s="366" t="s">
+      <c r="K20" s="360" t="s">
         <v>90</v>
       </c>
       <c r="L20" s="42" t="str">
@@ -5267,7 +5244,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="30.75" thickBot="1">
+    <row r="21" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="282">
         <v>46196</v>
       </c>
@@ -5292,13 +5269,13 @@
       <c r="H21" s="286" t="s">
         <v>32</v>
       </c>
-      <c r="I21" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="366" t="s">
+      <c r="I21" s="321" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="321" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="360" t="s">
         <v>90</v>
       </c>
       <c r="L21" s="67" t="str">
@@ -5306,7 +5283,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="279">
         <v>46226</v>
       </c>
@@ -5345,29 +5322,29 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="337">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="331">
         <v>46227</v>
       </c>
-      <c r="C23" s="338" t="str">
+      <c r="C23" s="332" t="str">
         <f>IF(ISNUMBER(FIND("?", B23, 1)), "TBD", TEXT(B23, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D23" s="339">
+      <c r="D23" s="333">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E23" s="339">
+      <c r="E23" s="333">
         <v>0.66666666666666663</v>
       </c>
       <c r="F23" s="221">
         <f>((E23 - D23) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G23" s="338">
+      <c r="G23" s="332">
         <f>IF(F23 &gt; 4, (F23 - 1), F23)</f>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H23" s="340" t="s">
+      <c r="H23" s="334" t="s">
         <v>4</v>
       </c>
       <c r="I23" s="199" t="s">
@@ -5376,7 +5353,7 @@
       <c r="J23" s="199" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="341" t="s">
+      <c r="K23" s="335" t="s">
         <v>46</v>
       </c>
       <c r="L23" s="59" t="str">
@@ -5384,7 +5361,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="140">
         <v>46232</v>
       </c>
@@ -5418,12 +5395,12 @@
       <c r="K24" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="L24" s="329" t="str">
+      <c r="L24" s="323" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="140">
         <v>46233</v>
       </c>
@@ -5457,34 +5434,34 @@
       <c r="K25" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="L25" s="329" t="str">
+      <c r="L25" s="323" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15.75" thickBot="1">
-      <c r="B26" s="330">
+    <row r="26" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="324">
         <v>46234</v>
       </c>
-      <c r="C26" s="331" t="str">
-        <f t="shared" ref="C26:C47" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
+      <c r="C26" s="325" t="str">
+        <f t="shared" ref="C26:C49" si="5">IF(ISNUMBER(FIND("?", B26, 1)), "TBD", TEXT(B26, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D26" s="332">
+      <c r="D26" s="326">
         <v>0.45833333333333331</v>
       </c>
-      <c r="E26" s="332">
+      <c r="E26" s="326">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F26" s="333">
-        <f t="shared" ref="F26:F44" si="6">((E26 - D26) * 24)</f>
+      <c r="F26" s="327">
+        <f t="shared" ref="F26:F46" si="6">((E26 - D26) * 24)</f>
         <v>5</v>
       </c>
-      <c r="G26" s="331">
-        <f t="shared" ref="G26:G47" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
-        <v>4</v>
-      </c>
-      <c r="H26" s="334" t="s">
+      <c r="G26" s="325">
+        <f t="shared" ref="G26:G49" si="7">IF(F26 &gt; 4, (F26 - 1), F26)</f>
+        <v>4</v>
+      </c>
+      <c r="H26" s="328" t="s">
         <v>4</v>
       </c>
       <c r="I26" s="244" t="s">
@@ -5493,15 +5470,15 @@
       <c r="J26" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="335" t="s">
+      <c r="K26" s="329" t="s">
         <v>59</v>
       </c>
-      <c r="L26" s="336" t="str">
-        <f t="shared" ref="L26:L47" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
-        <v>Passed</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12">
+      <c r="L26" s="330" t="str">
+        <f t="shared" ref="L26:L49" ca="1" si="8">IF(C26 = "TBD", "TBD", IF(B26 = "", "IDK!!", IF(TODAY() &gt; B26, "Passed", IF(TODAY() = B26, "Today!!", "Upcoming"))))</f>
+        <v>Passed</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="123">
         <v>46240</v>
       </c>
@@ -5540,7 +5517,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="249">
         <v>46241</v>
       </c>
@@ -5579,7 +5556,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="249">
         <v>46244</v>
       </c>
@@ -5618,7 +5595,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="249">
         <v>46245</v>
       </c>
@@ -5657,7 +5634,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="30">
+    <row r="31" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="249">
         <v>46246</v>
       </c>
@@ -5696,7 +5673,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:12" ht="30">
+    <row r="32" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B32" s="249">
         <v>46246</v>
       </c>
@@ -5735,7 +5712,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:16">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="250">
         <v>46247</v>
       </c>
@@ -5774,7 +5751,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:16">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="250">
         <v>46248</v>
       </c>
@@ -5813,7 +5790,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:16" ht="15.75" thickBot="1">
+    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="250">
         <v>46253</v>
       </c>
@@ -5852,7 +5829,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15.75" thickBot="1">
+    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="105">
         <v>46269</v>
       </c>
@@ -5891,45 +5868,45 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B37" s="322">
+    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="316">
         <v>46275</v>
       </c>
-      <c r="C37" s="323" t="str">
+      <c r="C37" s="317" t="str">
         <f t="shared" si="9"/>
         <v>Thu</v>
       </c>
-      <c r="D37" s="324">
+      <c r="D37" s="318">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E37" s="324">
+      <c r="E37" s="318">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F37" s="325">
+      <c r="F37" s="319">
         <f t="shared" si="10"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="317">
         <f t="shared" si="11"/>
         <v>0.99999999999999911</v>
       </c>
-      <c r="H37" s="326" t="s">
-        <v>4</v>
-      </c>
-      <c r="I37" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="327" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="328" t="s">
+      <c r="H37" s="320" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" s="321" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="321" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="322" t="s">
         <v>72</v>
       </c>
       <c r="L37" s="67" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>Passed</v>
       </c>
-      <c r="N37" s="342" t="s">
+      <c r="N37" s="336" t="s">
         <v>74</v>
       </c>
       <c r="O37" s="98" t="s">
@@ -5939,7 +5916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:16">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="107">
         <v>46275</v>
       </c>
@@ -5953,7 +5930,7 @@
       <c r="E38" s="162">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F38" s="367">
+      <c r="F38" s="361">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -5977,346 +5954,332 @@
         <f t="shared" ca="1" si="12"/>
         <v>Passed</v>
       </c>
-      <c r="N38" s="348" t="s">
+      <c r="N38" s="342" t="s">
         <v>76</v>
       </c>
-      <c r="O38" s="349">
+      <c r="O38" s="343">
         <v>2024</v>
       </c>
-      <c r="P38" s="350">
+      <c r="P38" s="344">
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B39" s="316">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="106">
         <v>46275</v>
       </c>
-      <c r="C39" s="317" t="str">
-        <f t="shared" ref="C39" si="13">IF(ISNUMBER(FIND("?", B39, 1)), "TBD", TEXT(B39, "ddd"))</f>
+      <c r="C39" s="171" t="str">
+        <f t="shared" ref="C39:C41" si="13">IF(ISNUMBER(FIND("?", B39, 1)), "TBD", TEXT(B39, "ddd"))</f>
         <v>Thu</v>
       </c>
-      <c r="D39" s="318">
+      <c r="D39" s="161">
         <v>0.5</v>
       </c>
-      <c r="E39" s="318">
+      <c r="E39" s="161">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F39" s="319">
-        <f t="shared" ref="F39:F41" si="14">((E39 - D39) * 24)</f>
+      <c r="F39" s="225">
+        <f t="shared" ref="F39:F43" si="14">((E39 - D39) * 24)</f>
         <v>3.9999999999999991</v>
       </c>
-      <c r="G39" s="317">
-        <f t="shared" ref="G39:G41" si="15">IF(F39 &gt; 4, (F39 - 1), F39)</f>
+      <c r="G39" s="171">
+        <f t="shared" ref="G39:G43" si="15">IF(F39 &gt; 4, (F39 - 1), F39)</f>
         <v>3.9999999999999991</v>
       </c>
-      <c r="H39" s="320" t="s">
+      <c r="H39" s="186" t="s">
         <v>32</v>
       </c>
-      <c r="I39" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="321" t="s">
+      <c r="I39" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="211" t="s">
         <v>93</v>
       </c>
-      <c r="L39" s="60" t="str">
-        <f t="shared" ref="L39:L41" ca="1" si="16">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
-        <v>Passed</v>
-      </c>
-      <c r="N39" s="351"/>
-      <c r="O39" s="352"/>
-      <c r="P39" s="353"/>
-    </row>
-    <row r="40" spans="2:16">
-      <c r="B40" s="295">
-        <v>46297</v>
-      </c>
-      <c r="C40" s="296" t="str">
-        <f>IF(ISNUMBER(FIND("?", B40, 1)), "TBD", TEXT(B40, "ddd"))</f>
-        <v>Fri</v>
-      </c>
-      <c r="D40" s="297">
+      <c r="L39" s="193" t="str">
+        <f t="shared" ref="L39:L43" ca="1" si="16">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
+        <v>Passed</v>
+      </c>
+      <c r="N39" s="345"/>
+      <c r="O39" s="346"/>
+      <c r="P39" s="347"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="316">
+        <v>46289</v>
+      </c>
+      <c r="C40" s="317" t="str">
+        <f t="shared" si="13"/>
+        <v>Thu</v>
+      </c>
+      <c r="D40" s="318">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E40" s="297">
+      <c r="E40" s="318">
         <v>0.375</v>
       </c>
-      <c r="F40" s="298">
+      <c r="F40" s="319">
         <f t="shared" si="14"/>
         <v>1.9999999999999996</v>
       </c>
-      <c r="G40" s="296">
+      <c r="G40" s="317">
         <f t="shared" si="15"/>
         <v>1.9999999999999996</v>
       </c>
-      <c r="H40" s="299" t="s">
+      <c r="H40" s="320" t="s">
         <v>32</v>
       </c>
-      <c r="I40" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="196" t="s">
+      <c r="I40" s="321" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="321" t="s">
         <v>28</v>
       </c>
-      <c r="K40" s="368" t="s">
+      <c r="K40" s="322" t="s">
+        <v>95</v>
+      </c>
+      <c r="L40" s="67" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v>Today!!</v>
+      </c>
+      <c r="N40" s="345"/>
+      <c r="O40" s="346"/>
+      <c r="P40" s="347"/>
+    </row>
+    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="107">
+        <v>46289</v>
+      </c>
+      <c r="C41" s="172" t="str">
+        <f t="shared" si="13"/>
+        <v>Thu</v>
+      </c>
+      <c r="D41" s="162">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E41" s="162">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="361">
+        <f t="shared" si="14"/>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="G41" s="172">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="H41" s="187" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="202" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="202" t="s">
+        <v>28</v>
+      </c>
+      <c r="K41" s="212" t="s">
+        <v>96</v>
+      </c>
+      <c r="L41" s="251" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v>Today!!</v>
+      </c>
+      <c r="N41" s="345"/>
+      <c r="O41" s="346"/>
+      <c r="P41" s="347"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="295">
+        <v>46297</v>
+      </c>
+      <c r="C42" s="296" t="str">
+        <f>IF(ISNUMBER(FIND("?", B42, 1)), "TBD", TEXT(B42, "ddd"))</f>
+        <v>Fri</v>
+      </c>
+      <c r="D42" s="297">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E42" s="297">
+        <v>0.375</v>
+      </c>
+      <c r="F42" s="298">
+        <f t="shared" si="14"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="G42" s="296">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="H42" s="299" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="196" t="s">
+        <v>28</v>
+      </c>
+      <c r="K42" s="362" t="s">
         <v>94</v>
       </c>
-      <c r="L40" s="42" t="str">
+      <c r="L42" s="42" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>Upcoming</v>
       </c>
-      <c r="N40" s="351"/>
-      <c r="O40" s="352"/>
-      <c r="P40" s="353"/>
-    </row>
-    <row r="41" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B41" s="369">
+      <c r="N42" s="345"/>
+      <c r="O42" s="346"/>
+      <c r="P42" s="347"/>
+    </row>
+    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="363">
         <v>46297</v>
       </c>
-      <c r="C41" s="370" t="str">
-        <f>IF(ISNUMBER(FIND("?", B41, 1)), "TBD", TEXT(B41, "ddd"))</f>
+      <c r="C43" s="364" t="str">
+        <f>IF(ISNUMBER(FIND("?", B43, 1)), "TBD", TEXT(B43, "ddd"))</f>
         <v>Fri</v>
       </c>
-      <c r="D41" s="371">
+      <c r="D43" s="365">
         <v>0.58333333333333337</v>
       </c>
-      <c r="E41" s="371">
+      <c r="E43" s="365">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F41" s="372">
+      <c r="F43" s="366">
         <f t="shared" si="14"/>
         <v>1.9999999999999982</v>
       </c>
-      <c r="G41" s="370">
+      <c r="G43" s="364">
         <f t="shared" si="15"/>
         <v>1.9999999999999982</v>
       </c>
-      <c r="H41" s="373" t="s">
+      <c r="H43" s="367" t="s">
         <v>32</v>
       </c>
-      <c r="I41" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="244" t="s">
+      <c r="I43" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="244" t="s">
         <v>28</v>
       </c>
-      <c r="K41" s="374" t="s">
+      <c r="K43" s="368" t="s">
         <v>94</v>
       </c>
-      <c r="L41" s="60" t="str">
+      <c r="L43" s="60" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>Upcoming</v>
       </c>
-      <c r="N41" s="351"/>
-      <c r="O41" s="352"/>
-      <c r="P41" s="353"/>
-    </row>
-    <row r="42" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B42" s="124">
+      <c r="N43" s="345"/>
+      <c r="O43" s="346"/>
+      <c r="P43" s="347"/>
+    </row>
+    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="124">
         <v>46353</v>
       </c>
-      <c r="C42" s="173" t="str">
+      <c r="C44" s="173" t="str">
         <f t="shared" si="5"/>
         <v>Fri</v>
       </c>
-      <c r="D42" s="155">
+      <c r="D44" s="155">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E42" s="155">
+      <c r="E44" s="155">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F42" s="226">
+      <c r="F44" s="226">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G42" s="173">
+      <c r="G44" s="173">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H42" s="188" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="200" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="269" t="s">
+      <c r="H44" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="L42" s="192" t="str">
+      <c r="L44" s="192" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N42" s="351" t="s">
+      <c r="N44" s="345" t="s">
         <v>77</v>
       </c>
-      <c r="O42" s="352">
+      <c r="O44" s="346">
         <f>O38+1</f>
         <v>2025</v>
       </c>
-      <c r="P42" s="353">
+      <c r="P44" s="347">
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="2:16">
-      <c r="B43" s="112">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B45" s="112">
         <v>46380</v>
       </c>
-      <c r="C43" s="264" t="str">
+      <c r="C45" s="264" t="str">
         <f t="shared" si="5"/>
         <v>Thu</v>
       </c>
-      <c r="D43" s="262">
+      <c r="D45" s="262">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E43" s="262">
+      <c r="E45" s="262">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F43" s="263">
+      <c r="F45" s="263">
         <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
-      <c r="G43" s="264">
+      <c r="G45" s="264">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H43" s="265" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="196" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="266" t="s">
+      <c r="H45" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="266" t="s">
         <v>60</v>
       </c>
-      <c r="L43" s="42" t="str">
+      <c r="L45" s="42" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N43" s="343" t="s">
+      <c r="N45" s="337" t="s">
         <v>78</v>
       </c>
-      <c r="O43" s="70">
-        <f>O42+1</f>
+      <c r="O45" s="70">
+        <f>O44+1</f>
         <v>2026</v>
       </c>
-      <c r="P43" s="344">
+      <c r="P45" s="338">
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="2:16">
-      <c r="B44" s="120">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B46" s="120">
         <v>46384</v>
       </c>
-      <c r="C44" s="274" t="str">
+      <c r="C46" s="274" t="str">
         <f t="shared" si="5"/>
         <v>Mon</v>
       </c>
-      <c r="D44" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E44" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F44" s="276">
-        <f t="shared" si="6"/>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G44" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H44" s="277" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="199" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="278" t="s">
-        <v>60</v>
-      </c>
-      <c r="L44" s="59" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="N44" s="343" t="s">
-        <v>79</v>
-      </c>
-      <c r="O44" s="70">
-        <f t="shared" ref="O44:O50" si="17">O43+1</f>
-        <v>2027</v>
-      </c>
-      <c r="P44" s="344">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16">
-      <c r="B45" s="270">
-        <v>46385</v>
-      </c>
-      <c r="C45" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Tue</v>
-      </c>
-      <c r="D45" s="275">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E45" s="275">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F45" s="276">
-        <f t="shared" ref="F45:F47" si="18">((E45 - D45) * 24)</f>
-        <v>8.9999999999999982</v>
-      </c>
-      <c r="G45" s="274">
-        <f t="shared" si="7"/>
-        <v>7.9999999999999982</v>
-      </c>
-      <c r="H45" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J45" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="273" t="s">
-        <v>60</v>
-      </c>
-      <c r="L45" s="193" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="N45" s="343" t="s">
-        <v>80</v>
-      </c>
-      <c r="O45" s="70">
-        <f t="shared" si="17"/>
-        <v>2028</v>
-      </c>
-      <c r="P45" s="344">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16">
-      <c r="B46" s="270">
-        <v>46386</v>
-      </c>
-      <c r="C46" s="271" t="str">
-        <f t="shared" si="5"/>
-        <v>Wed</v>
-      </c>
       <c r="D46" s="275">
         <v>0.29166666666666669</v>
       </c>
@@ -6324,47 +6287,47 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F46" s="276">
-        <f t="shared" si="18"/>
+        <f t="shared" si="6"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G46" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H46" s="272" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="198" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="273" t="s">
+      <c r="H46" s="277" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="199" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="L46" s="193" t="str">
+      <c r="L46" s="59" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N46" s="343" t="s">
-        <v>81</v>
+      <c r="N46" s="337" t="s">
+        <v>79</v>
       </c>
       <c r="O46" s="70">
-        <f t="shared" si="17"/>
-        <v>2029</v>
-      </c>
-      <c r="P46" s="344">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B47" s="113">
-        <v>46387</v>
+        <f t="shared" ref="O46:O52" si="17">O45+1</f>
+        <v>2027</v>
+      </c>
+      <c r="P46" s="338">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B47" s="270">
+        <v>46385</v>
       </c>
       <c r="C47" s="271" t="str">
         <f t="shared" si="5"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="D47" s="275">
         <v>0.29166666666666669</v>
@@ -6373,159 +6336,257 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F47" s="276">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F47:F49" si="18">((E47 - D47) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G47" s="274">
         <f t="shared" si="7"/>
         <v>7.9999999999999982</v>
       </c>
-      <c r="H47" s="267" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" s="244" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="268" t="s">
+      <c r="H47" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="273" t="s">
         <v>60</v>
       </c>
       <c r="L47" s="193" t="str">
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N47" s="343" t="s">
-        <v>82</v>
+      <c r="N47" s="337" t="s">
+        <v>80</v>
       </c>
       <c r="O47" s="70">
         <f t="shared" si="17"/>
-        <v>2030</v>
-      </c>
-      <c r="P47" s="344">
+        <v>2028</v>
+      </c>
+      <c r="P47" s="338">
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="2:16">
-      <c r="B48" s="102"/>
-      <c r="C48" s="165" t="str">
-        <f t="shared" ref="C48:C49" si="19">IF(ISNUMBER(FIND("?", B48, 1)), "TBD", TEXT(B48, "ddd"))</f>
-        <v>Sat</v>
-      </c>
-      <c r="D48" s="157"/>
-      <c r="E48" s="157"/>
-      <c r="F48" s="220">
-        <f t="shared" ref="F48:F49" si="20">((E48 - D48) * 24)</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="217">
-        <f t="shared" ref="G48:G49" si="21">IF(F48 &gt; 4, (F48 - 1), F48)</f>
-        <v>0</v>
-      </c>
-      <c r="H48" s="180"/>
-      <c r="I48" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="J48" s="197" t="s">
-        <v>66</v>
-      </c>
-      <c r="K48" s="205"/>
-      <c r="L48" s="252" t="str">
-        <f t="shared" ref="L48:L49" ca="1" si="22">IF(C48 = "TBD", "TBD", IF(B48 = "", "IDK!!", IF(TODAY() &gt; B48, "Passed", IF(TODAY() = B48, "Today!!", "Upcoming"))))</f>
-        <v>IDK!!</v>
-      </c>
-      <c r="N48" s="343" t="s">
-        <v>83</v>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B48" s="270">
+        <v>46386</v>
+      </c>
+      <c r="C48" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Wed</v>
+      </c>
+      <c r="D48" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E48" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F48" s="276">
+        <f t="shared" si="18"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G48" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H48" s="272" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="198" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="273" t="s">
+        <v>60</v>
+      </c>
+      <c r="L48" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="N48" s="337" t="s">
+        <v>81</v>
       </c>
       <c r="O48" s="70">
         <f t="shared" si="17"/>
+        <v>2029</v>
+      </c>
+      <c r="P48" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="113">
+        <v>46387</v>
+      </c>
+      <c r="C49" s="271" t="str">
+        <f t="shared" si="5"/>
+        <v>Thu</v>
+      </c>
+      <c r="D49" s="275">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E49" s="275">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F49" s="276">
+        <f t="shared" si="18"/>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="G49" s="274">
+        <f t="shared" si="7"/>
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="H49" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="244" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L49" s="193" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>Upcoming</v>
+      </c>
+      <c r="N49" s="337" t="s">
+        <v>82</v>
+      </c>
+      <c r="O49" s="70">
+        <f t="shared" si="17"/>
+        <v>2030</v>
+      </c>
+      <c r="P49" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="102"/>
+      <c r="C50" s="165" t="str">
+        <f t="shared" ref="C50:C51" si="19">IF(ISNUMBER(FIND("?", B50, 1)), "TBD", TEXT(B50, "ddd"))</f>
+        <v>Sat</v>
+      </c>
+      <c r="D50" s="157"/>
+      <c r="E50" s="157"/>
+      <c r="F50" s="220">
+        <f t="shared" ref="F50:F51" si="20">((E50 - D50) * 24)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="217">
+        <f t="shared" ref="G50:G51" si="21">IF(F50 &gt; 4, (F50 - 1), F50)</f>
+        <v>0</v>
+      </c>
+      <c r="H50" s="180"/>
+      <c r="I50" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="J50" s="197" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50" s="205"/>
+      <c r="L50" s="252" t="str">
+        <f t="shared" ref="L50:L51" ca="1" si="22">IF(C50 = "TBD", "TBD", IF(B50 = "", "IDK!!", IF(TODAY() &gt; B50, "Passed", IF(TODAY() = B50, "Today!!", "Upcoming"))))</f>
+        <v>IDK!!</v>
+      </c>
+      <c r="N50" s="337" t="s">
+        <v>83</v>
+      </c>
+      <c r="O50" s="70">
+        <f t="shared" si="17"/>
         <v>2031</v>
       </c>
-      <c r="P48" s="344">
+      <c r="P50" s="338">
         <v>176</v>
       </c>
     </row>
-    <row r="49" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B49" s="259"/>
-      <c r="C49" s="253" t="str">
+    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="259"/>
+      <c r="C51" s="253" t="str">
         <f t="shared" si="19"/>
         <v>Sat</v>
       </c>
-      <c r="D49" s="260"/>
-      <c r="E49" s="260"/>
-      <c r="F49" s="261">
+      <c r="D51" s="260"/>
+      <c r="E51" s="260"/>
+      <c r="F51" s="261">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="G49" s="253">
+      <c r="G51" s="253">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H49" s="254"/>
-      <c r="I49" s="202" t="s">
+      <c r="H51" s="254"/>
+      <c r="I51" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="J49" s="202" t="s">
+      <c r="J51" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="K49" s="255"/>
-      <c r="L49" s="251" t="str">
+      <c r="K51" s="255"/>
+      <c r="L51" s="251" t="str">
         <f t="shared" ca="1" si="22"/>
         <v>IDK!!</v>
       </c>
-      <c r="N49" s="343" t="s">
+      <c r="N51" s="337" t="s">
         <v>84</v>
       </c>
-      <c r="O49" s="70">
+      <c r="O51" s="70">
         <f t="shared" si="17"/>
         <v>2032</v>
       </c>
-      <c r="P49" s="344">
+      <c r="P51" s="338">
         <v>176</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B50" s="86" t="s">
+    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="303"/>
-      <c r="D50" s="304"/>
-      <c r="E50" s="305"/>
-      <c r="F50" s="228">
-        <f>SUM(F14:F49)</f>
-        <v>183.5</v>
-      </c>
-      <c r="G50" s="256">
-        <f>SUM(G14:G49)</f>
-        <v>160.5</v>
-      </c>
-      <c r="H50" s="301"/>
-      <c r="I50" s="302"/>
-      <c r="J50" s="302"/>
-      <c r="K50" s="302"/>
-      <c r="L50" s="302"/>
-      <c r="N50" s="345" t="s">
+      <c r="C52" s="303"/>
+      <c r="D52" s="304"/>
+      <c r="E52" s="305"/>
+      <c r="F52" s="228">
+        <f>SUM(F14:F51)</f>
+        <v>187.5</v>
+      </c>
+      <c r="G52" s="256">
+        <f>SUM(G14:G51)</f>
+        <v>164.5</v>
+      </c>
+      <c r="H52" s="301"/>
+      <c r="I52" s="302"/>
+      <c r="J52" s="302"/>
+      <c r="K52" s="302"/>
+      <c r="L52" s="302"/>
+      <c r="N52" s="339" t="s">
         <v>85</v>
       </c>
-      <c r="O50" s="346">
+      <c r="O52" s="340">
         <f t="shared" si="17"/>
         <v>2033</v>
       </c>
-      <c r="P50" s="347">
+      <c r="P52" s="341">
         <f>192 + 10</f>
         <v>202</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B13:K50" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
+  <autoFilter ref="B13:K52" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B14:L49">
+  <conditionalFormatting sqref="B14:L51">
     <cfRule type="expression" dxfId="20" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F49 L14:L49">
+  <conditionalFormatting sqref="C14:F51 L14:L51">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
@@ -6540,7 +6601,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J49">
+  <conditionalFormatting sqref="I14:J51">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
@@ -6557,7 +6618,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD57EB3B-515A-4E94-895F-88D262D477C2}">
   <dimension ref="B1:H44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -6567,8 +6628,8 @@
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:8" ht="18" thickBot="1">
+    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -6582,7 +6643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -6603,7 +6664,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -6614,7 +6675,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:8" ht="15.75" thickBot="1">
+    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -6631,7 +6692,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -6647,7 +6708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.75" thickBot="1">
+    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -6664,7 +6725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -6681,7 +6742,7 @@
       </c>
       <c r="G8" s="51"/>
     </row>
-    <row r="9" spans="2:8" ht="15.75" thickBot="1">
+    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -6698,7 +6759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -6715,7 +6776,7 @@
       </c>
       <c r="G10" s="36"/>
     </row>
-    <row r="11" spans="2:8" ht="15.75" thickBot="1">
+    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -6733,8 +6794,8 @@
       </c>
       <c r="G11" s="36"/>
     </row>
-    <row r="12" spans="2:8" ht="15.75" thickBot="1"/>
-    <row r="13" spans="2:8" ht="35.25" thickBot="1">
+    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -6757,7 +6818,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15.75" thickBot="1">
+    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="133">
         <v>45743</v>
       </c>
@@ -6782,7 +6843,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="102">
         <v>45783</v>
       </c>
@@ -6807,7 +6868,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="140">
         <v>45797</v>
       </c>
@@ -6832,7 +6893,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15.75" thickBot="1">
+    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="137">
         <v>45800</v>
       </c>
@@ -6857,7 +6918,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15.75" thickBot="1">
+    <row r="18" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="148">
         <v>45827</v>
       </c>
@@ -6882,7 +6943,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15.75" thickBot="1">
+    <row r="19" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="143">
         <v>45849</v>
       </c>
@@ -6907,7 +6968,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="105">
         <v>45873</v>
       </c>
@@ -6932,7 +6993,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="106">
         <v>45874</v>
       </c>
@@ -6957,7 +7018,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="106">
         <v>45875</v>
       </c>
@@ -6982,7 +7043,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="106">
         <v>45876</v>
       </c>
@@ -7007,7 +7068,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="106">
         <v>45877</v>
       </c>
@@ -7032,7 +7093,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="106">
         <v>45880</v>
       </c>
@@ -7057,7 +7118,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="106">
         <v>45880</v>
       </c>
@@ -7082,7 +7143,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="106">
         <v>45881</v>
       </c>
@@ -7107,7 +7168,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="106">
         <v>45882</v>
       </c>
@@ -7132,7 +7193,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="106">
         <v>45883</v>
       </c>
@@ -7157,7 +7218,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="107">
         <v>45884</v>
       </c>
@@ -7182,7 +7243,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="107">
         <v>45884</v>
       </c>
@@ -7207,7 +7268,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="107">
         <v>45884</v>
       </c>
@@ -7232,7 +7293,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="107">
         <v>45889</v>
       </c>
@@ -7257,7 +7318,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="15.75" thickBot="1">
+    <row r="34" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="107">
         <v>45898</v>
       </c>
@@ -7282,7 +7343,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15.75" thickBot="1">
+    <row r="35" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="124">
         <v>45908</v>
       </c>
@@ -7307,7 +7368,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15.75" thickBot="1">
+    <row r="36" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="108">
         <v>45989</v>
       </c>
@@ -7332,7 +7393,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="109">
         <v>46014</v>
       </c>
@@ -7357,7 +7418,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="110">
         <v>46015</v>
       </c>
@@ -7382,7 +7443,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="110">
         <v>46017</v>
       </c>
@@ -7407,7 +7468,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="111">
         <v>46020</v>
       </c>
@@ -7432,7 +7493,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="111">
         <v>46021</v>
       </c>
@@ -7457,7 +7518,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15.75" thickBot="1">
+    <row r="42" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="111">
         <v>46022</v>
       </c>
@@ -7482,7 +7543,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="15.75" thickBot="1">
+    <row r="43" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="124">
         <v>46024</v>
       </c>
@@ -7507,7 +7568,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15.75" thickBot="1">
+    <row r="44" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
         <v>11</v>
       </c>
@@ -7552,7 +7613,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D12B9BF-3416-48A7-87E4-2977D80A472D}">
   <dimension ref="B1:K48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -7565,8 +7626,8 @@
     <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:11" ht="18" thickBot="1">
+    <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -7580,7 +7641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -7601,7 +7662,7 @@
         <v>PTO Reset: 02/12/2026</v>
       </c>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -7612,7 +7673,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:11" ht="15.75" thickBot="1">
+    <row r="5" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -7629,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -7645,7 +7706,7 @@
         <v>8.5000000000000071</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="15.75" thickBot="1">
+    <row r="7" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -7662,7 +7723,7 @@
         <v>1.0625000000000009</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -7679,7 +7740,7 @@
       </c>
       <c r="J8" s="51"/>
     </row>
-    <row r="9" spans="2:11" ht="15.75" thickBot="1">
+    <row r="9" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -7696,7 +7757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -7713,7 +7774,7 @@
       </c>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="2:11" ht="15.75" thickBot="1">
+    <row r="11" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -7731,8 +7792,8 @@
       </c>
       <c r="J11" s="36"/>
     </row>
-    <row r="12" spans="2:11" ht="15.75" thickBot="1"/>
-    <row r="13" spans="2:11" ht="35.25" thickBot="1">
+    <row r="12" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:11" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -7764,7 +7825,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="15.75" thickBot="1">
+    <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="133">
         <v>45743</v>
       </c>
@@ -7800,7 +7861,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="102">
         <v>45783</v>
       </c>
@@ -7836,7 +7897,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="140">
         <v>45797</v>
       </c>
@@ -7872,7 +7933,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.75" thickBot="1">
+    <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="137">
         <v>45800</v>
       </c>
@@ -7908,7 +7969,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="15.75" thickBot="1">
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="148">
         <v>45827</v>
       </c>
@@ -7944,7 +8005,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.75" thickBot="1">
+    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="143">
         <v>45849</v>
       </c>
@@ -7980,7 +8041,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="105">
         <v>45873</v>
       </c>
@@ -8016,7 +8077,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="106">
         <v>45874</v>
       </c>
@@ -8052,7 +8113,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="106">
         <v>45875</v>
       </c>
@@ -8088,7 +8149,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="106">
         <v>45876</v>
       </c>
@@ -8124,7 +8185,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:11">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="106">
         <v>45877</v>
       </c>
@@ -8160,7 +8221,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:11">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="106">
         <v>45880</v>
       </c>
@@ -8196,7 +8257,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:11">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="106">
         <v>45880</v>
       </c>
@@ -8232,7 +8293,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="27" spans="2:11">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="106">
         <v>45881</v>
       </c>
@@ -8268,7 +8329,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="106">
         <v>45882</v>
       </c>
@@ -8304,7 +8365,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:11">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="106">
         <v>45883</v>
       </c>
@@ -8340,7 +8401,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="107">
         <v>45884</v>
       </c>
@@ -8376,7 +8437,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="107">
         <v>45884</v>
       </c>
@@ -8412,7 +8473,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="107">
         <v>45884</v>
       </c>
@@ -8448,7 +8509,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="107">
         <v>45889</v>
       </c>
@@ -8484,7 +8545,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="107">
         <v>45898</v>
       </c>
@@ -8520,7 +8581,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.75" thickBot="1">
+    <row r="35" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="148">
         <v>45908</v>
       </c>
@@ -8556,7 +8617,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="229">
         <v>45933</v>
       </c>
@@ -8592,7 +8653,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="15.75" thickBot="1">
+    <row r="37" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="282">
         <v>45936</v>
       </c>
@@ -8628,7 +8689,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.75" thickBot="1">
+    <row r="38" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="289">
         <v>45989</v>
       </c>
@@ -8664,7 +8725,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="295">
         <v>45999</v>
       </c>
@@ -8700,7 +8761,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="234">
         <v>46006</v>
       </c>
@@ -8736,7 +8797,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="234">
         <v>46014</v>
       </c>
@@ -8772,7 +8833,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="42" spans="2:11">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="234">
         <v>46015</v>
       </c>
@@ -8808,7 +8869,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="43" spans="2:11">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="110">
         <v>46017</v>
       </c>
@@ -8844,7 +8905,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="44" spans="2:11">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="111">
         <v>46020</v>
       </c>
@@ -8880,7 +8941,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="45" spans="2:11">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="111">
         <v>46021</v>
       </c>
@@ -8916,7 +8977,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="46" spans="2:11" ht="15.75" thickBot="1">
+    <row r="46" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="111">
         <v>46022</v>
       </c>
@@ -8952,7 +9013,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="47" spans="2:11" ht="15.75" thickBot="1">
+    <row r="47" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="124">
         <v>46024</v>
       </c>
@@ -8988,7 +9049,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="48" spans="2:11" ht="15.75" thickBot="1">
+    <row r="48" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="6" t="s">
         <v>11</v>
       </c>
@@ -9045,7 +9106,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25002DC1-579B-4118-A464-8DA972BBC903}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:G43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
@@ -9056,8 +9117,8 @@
     <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1">
+    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -9075,7 +9136,7 @@
         <v>PTO Reset: 02/12/2025</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -9091,7 +9152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="15.75" thickBot="1">
+    <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
@@ -9108,7 +9169,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>15</v>
       </c>
@@ -9125,7 +9186,7 @@
       </c>
       <c r="G5" s="55"/>
     </row>
-    <row r="6" spans="2:7" ht="15.75" thickBot="1">
+    <row r="6" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
         <v>16</v>
       </c>
@@ -9143,7 +9204,7 @@
       </c>
       <c r="G6" s="36"/>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
@@ -9159,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="15.75" thickBot="1">
+    <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
@@ -9177,7 +9238,7 @@
       </c>
       <c r="G8" s="36"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="127" t="s">
         <v>22</v>
       </c>
@@ -9194,7 +9255,7 @@
       </c>
       <c r="G9" s="36"/>
     </row>
-    <row r="10" spans="2:7" ht="15.75" thickBot="1">
+    <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="130" t="s">
         <v>23</v>
       </c>
@@ -9212,8 +9273,8 @@
       </c>
       <c r="G10" s="36"/>
     </row>
-    <row r="11" spans="2:7" ht="15.75" thickBot="1"/>
-    <row r="12" spans="2:7" ht="35.25" thickBot="1">
+    <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:7" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="28" t="s">
         <v>1</v>
       </c>
@@ -9233,7 +9294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="30">
+    <row r="13" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="112">
         <v>45436</v>
       </c>
@@ -9254,7 +9315,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15.75" thickBot="1">
+    <row r="14" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="113">
         <v>45443</v>
       </c>
@@ -9275,7 +9336,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15.75" thickBot="1">
+    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="114">
         <v>45499</v>
       </c>
@@ -9296,7 +9357,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="115">
         <v>45509</v>
       </c>
@@ -9317,7 +9378,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="116">
         <v>45510</v>
       </c>
@@ -9338,7 +9399,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="116">
         <v>45511</v>
       </c>
@@ -9359,7 +9420,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="116">
         <v>45512</v>
       </c>
@@ -9380,7 +9441,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="116">
         <v>45513</v>
       </c>
@@ -9401,7 +9462,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="117">
         <v>45516</v>
       </c>
@@ -9422,7 +9483,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="117">
         <v>45517</v>
       </c>
@@ -9443,7 +9504,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="117">
         <v>45518</v>
       </c>
@@ -9464,7 +9525,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="117">
         <v>45519</v>
       </c>
@@ -9485,7 +9546,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="118">
         <v>45520</v>
       </c>
@@ -9506,7 +9567,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="116">
         <v>45525</v>
       </c>
@@ -9527,7 +9588,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="116">
         <v>45530</v>
       </c>
@@ -9548,7 +9609,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15.75" thickBot="1">
+    <row r="28" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="119">
         <v>45534</v>
       </c>
@@ -9569,7 +9630,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="112">
         <v>45567</v>
       </c>
@@ -9590,7 +9651,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="120">
         <v>45573</v>
       </c>
@@ -9611,7 +9672,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="121">
         <v>45579</v>
       </c>
@@ -9632,7 +9693,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="15.75" thickBot="1">
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="113">
         <v>45580</v>
       </c>
@@ -9653,7 +9714,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="103">
         <v>45597</v>
       </c>
@@ -9674,7 +9735,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="15.75" thickBot="1">
+    <row r="34" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="104">
         <v>45625</v>
       </c>
@@ -9695,7 +9756,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="122">
         <v>45653</v>
       </c>
@@ -9716,7 +9777,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="123">
         <v>45656</v>
       </c>
@@ -9737,7 +9798,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="123">
         <v>45657</v>
       </c>
@@ -9758,7 +9819,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="123">
         <v>45659</v>
       </c>
@@ -9779,7 +9840,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="123">
         <v>45660</v>
       </c>
@@ -9800,7 +9861,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="123">
         <v>45663</v>
       </c>
@@ -9821,7 +9882,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="123">
         <v>45664</v>
       </c>
@@ -9842,7 +9903,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="15.75" thickBot="1">
+    <row r="42" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="114">
         <v>45665</v>
       </c>
@@ -9863,7 +9924,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="15.75" thickBot="1">
+    <row r="43" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="86" t="s">
         <v>11</v>
       </c>
@@ -9915,7 +9976,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8D74E6-E2F4-497A-863D-7746D04C8BB1}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:G22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -9925,8 +9986,8 @@
     <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1">
+    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -9940,7 +10001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -9961,7 +10022,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -9972,7 +10033,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:7" ht="15.75" thickBot="1">
+    <row r="5" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -9989,7 +10050,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -10005,7 +10066,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="15.75" thickBot="1">
+    <row r="7" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -10022,7 +10083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -10039,7 +10100,7 @@
       </c>
       <c r="G8" s="51"/>
     </row>
-    <row r="9" spans="2:7" ht="15.75" thickBot="1">
+    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -10056,7 +10117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -10073,7 +10134,7 @@
       </c>
       <c r="G10" s="36"/>
     </row>
-    <row r="11" spans="2:7" ht="15.75" thickBot="1">
+    <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -10091,8 +10152,8 @@
       </c>
       <c r="G11" s="36"/>
     </row>
-    <row r="12" spans="2:7" ht="15.75" thickBot="1"/>
-    <row r="13" spans="2:7" ht="35.25" thickBot="1">
+    <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:7" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -10112,7 +10173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="38">
         <v>45658</v>
       </c>
@@ -10129,7 +10190,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15.75" thickBot="1">
+    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="31">
         <v>45658</v>
       </c>
@@ -10146,7 +10207,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15.75" thickBot="1">
+    <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
@@ -10159,22 +10220,22 @@
       <c r="F16" s="27"/>
       <c r="G16" s="20"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>33</v>
       </c>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\storage\I_Scratch\Git_Repository\PubRepo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01938263-0121-4A4B-B71E-9D702133C310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988B413E-B41A-4CBE-86BC-C17C4497378D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21615" yWindow="0" windowWidth="16830" windowHeight="13350" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="2175" yWindow="105" windowWidth="33285" windowHeight="20625" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -33,19 +33,30 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -60,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="97">
   <si>
     <t>Total</t>
   </si>
@@ -373,7 +384,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
     <numFmt numFmtId="165" formatCode="mm\/dd\/yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2556,7 +2567,316 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="53">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2771,65 +3091,6 @@
         <color theme="0" tint="-0.34998626667073579"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2845,50 +3106,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>104213</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>33058</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>557336</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>81149</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E248C3E9-F834-4D64-929C-81E8E2BE83A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15296588" y="233083"/>
-          <a:ext cx="2891523" cy="7473669"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>18</xdr:col>
@@ -2916,7 +3133,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2960,7 +3177,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2987,8 +3204,8 @@
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>178174</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>5603</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>173692</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3004,7 +3221,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3019,6 +3236,50 @@
         <a:xfrm>
           <a:off x="17720423" y="9378203"/>
           <a:ext cx="6441701" cy="3714750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>441917</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14474</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8E4D2A9-6F29-4694-B643-3FDBE6CB811B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15183971" y="201706"/>
+          <a:ext cx="2873593" cy="7488797"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3084,8 +3345,8 @@
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>185237</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>577443</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>190161</xdr:rowOff>
     </xdr:to>
@@ -3128,8 +3389,8 @@
       <xdr:rowOff>56029</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>558202</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>345290</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>140563</xdr:rowOff>
     </xdr:to>
@@ -3167,22 +3428,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:colOff>582706</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>178175</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>5603</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>458321</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>16809</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{598EE03C-087D-4905-8357-9B963760ED01}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A550F1BD-670D-4CBF-B9D3-9E9719CC6188}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3204,8 +3465,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15015323" y="9502028"/>
-          <a:ext cx="6464674" cy="3714750"/>
+          <a:off x="18691412" y="6129618"/>
+          <a:ext cx="6419850" cy="3714750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3966,9 +4227,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4006,7 +4267,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4112,7 +4373,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4254,7 +4515,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4262,8 +4523,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2671213-B148-403C-9F48-0EB30902282E}">
-  <dimension ref="B1:W20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:W43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -4276,14 +4537,17 @@
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="57" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.140625" customWidth="1"/>
     <col min="21" max="21" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:12" ht="18" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -4296,29 +4560,33 @@
       <c r="E2" s="18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K2" cm="1">
+        <f t="array" aca="1" ref="K2" ca="1">INT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"))</f>
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3">
-        <f ca="1">160+C4</f>
-        <v>180</v>
+        <f>160</f>
+        <v>160</v>
       </c>
       <c r="D3" s="3">
-        <f ca="1">C3-E3</f>
+        <f ca="1">SUM(C3 + C4) - E3</f>
         <v>56</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
+        <f ca="1">SUM(C3 + C4) - C6 - SUMIF(H14:H19, "PTO", G14:G19)</f>
         <v>124</v>
       </c>
-      <c r="K3" s="56" t="str" cm="1">
-        <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename", A2),LEN(CELL("filename", A2)) - SEARCH("]", CELL("filename", A2)))) + 1</f>
+      <c r="K3" s="56" t="str">
+        <f ca="1">"PTO Reset: 02/12/" &amp; INT(K2) + 1</f>
         <v>PTO Reset: 02/12/2028</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -4329,24 +4597,24 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="15.75" thickBot="1">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="7">
-        <f ca="1">C3/8</f>
+        <f ca="1">SUM(C3 + C4) / 8</f>
         <v>22.5</v>
       </c>
       <c r="D5" s="7">
-        <f ca="1">D3/8</f>
+        <f ca="1">D3 / 8</f>
         <v>7</v>
       </c>
       <c r="E5" s="8">
-        <f ca="1">E3/8</f>
+        <f ca="1">E3 / 8</f>
         <v>15.5</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -4354,7 +4622,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="10">
-        <f>C6-E6</f>
+        <f>C6  -E6</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
@@ -4362,24 +4630,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="15.75" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="13">
-        <f>C6/8</f>
+        <f>C6 / 8</f>
         <v>5</v>
       </c>
       <c r="D7" s="13">
-        <f>D6/8</f>
+        <f>D6 / 8</f>
         <v>0</v>
       </c>
       <c r="E7" s="14">
-        <f>E6/8</f>
+        <f>E6 / 8</f>
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -4387,7 +4655,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="2">
-        <f>C8-E8</f>
+        <f>C8 - E8</f>
         <v>0</v>
       </c>
       <c r="E8" s="1">
@@ -4396,24 +4664,24 @@
       </c>
       <c r="K8" s="51"/>
     </row>
-    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="7">
-        <f>C8/8</f>
+        <f>C8 / 8</f>
         <v>2</v>
       </c>
       <c r="D9" s="7">
-        <f>D8/8</f>
+        <f>D8 / 8</f>
         <v>0</v>
       </c>
       <c r="E9" s="15">
-        <f>E8/8</f>
+        <f>E8 / 8</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -4421,7 +4689,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="128">
-        <f>C10-E10</f>
+        <f>C10 - E10</f>
         <v>0</v>
       </c>
       <c r="E10" s="129">
@@ -4430,26 +4698,26 @@
       </c>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" ht="15.75" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="131">
-        <f>C10/8</f>
+        <f>C10 / 8</f>
         <v>0.5</v>
       </c>
       <c r="D11" s="131">
-        <f>D10/8</f>
+        <f>D10 / 8</f>
         <v>0</v>
       </c>
       <c r="E11" s="132">
-        <f>E10/8</f>
+        <f>E10 / 8</f>
         <v>0.5</v>
       </c>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:12" ht="35.25" thickBot="1">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -4484,7 +4752,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12">
       <c r="B14" s="122"/>
       <c r="C14" s="240" t="str">
         <f t="shared" ref="C14:C19" si="0">IF(ISNUMBER(FIND("?", B14, 1)), "TBD", TEXT(B14, "ddd"))</f>
@@ -4513,7 +4781,7 @@
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" ht="15.75" thickBot="1">
       <c r="B15" s="306"/>
       <c r="C15" s="307" t="str">
         <f t="shared" si="0"/>
@@ -4542,7 +4810,7 @@
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12">
       <c r="B16" s="282">
         <v>46717</v>
       </c>
@@ -4581,7 +4849,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="17" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:23" ht="15.75" thickBot="1">
       <c r="B17" s="104">
         <v>46720</v>
       </c>
@@ -4620,7 +4888,7 @@
         <v>Upcoming</v>
       </c>
     </row>
-    <row r="18" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:23" ht="15.75" thickBot="1">
       <c r="B18" s="102"/>
       <c r="C18" s="165" t="str">
         <f t="shared" si="0"/>
@@ -4660,7 +4928,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="19" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:23" ht="15.75" thickBot="1">
       <c r="B19" s="259"/>
       <c r="C19" s="253" t="str">
         <f t="shared" si="0"/>
@@ -4689,7 +4957,7 @@
         <v>IDK!!</v>
       </c>
     </row>
-    <row r="20" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:23" ht="15.75" thickBot="1">
       <c r="B20" s="86" t="s">
         <v>11</v>
       </c>
@@ -4710,33 +4978,156 @@
       <c r="K20" s="302"/>
       <c r="L20" s="302"/>
     </row>
+    <row r="32" spans="2:23" ht="15.75" thickBot="1"/>
+    <row r="33" spans="19:21" ht="15.75" thickBot="1">
+      <c r="S33" s="336" t="s">
+        <v>74</v>
+      </c>
+      <c r="T33" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="U33" s="200" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="19:21">
+      <c r="S34" s="342" t="s">
+        <v>76</v>
+      </c>
+      <c r="T34" s="343">
+        <v>2024</v>
+      </c>
+      <c r="U34" s="344">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="19:21">
+      <c r="S35" s="345" t="s">
+        <v>77</v>
+      </c>
+      <c r="T35" s="346">
+        <v>2025</v>
+      </c>
+      <c r="U35" s="347">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="19:21">
+      <c r="S36" s="337" t="s">
+        <v>78</v>
+      </c>
+      <c r="T36" s="70">
+        <v>2026</v>
+      </c>
+      <c r="U36" s="338">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="19:21">
+      <c r="S37" s="337" t="s">
+        <v>79</v>
+      </c>
+      <c r="T37" s="70">
+        <v>2027</v>
+      </c>
+      <c r="U37" s="338">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="19:21">
+      <c r="S38" s="337" t="s">
+        <v>80</v>
+      </c>
+      <c r="T38" s="70">
+        <v>2028</v>
+      </c>
+      <c r="U38" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="19:21">
+      <c r="S39" s="337" t="s">
+        <v>81</v>
+      </c>
+      <c r="T39" s="70">
+        <v>2029</v>
+      </c>
+      <c r="U39" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="19:21">
+      <c r="S40" s="337" t="s">
+        <v>82</v>
+      </c>
+      <c r="T40" s="70">
+        <v>2030</v>
+      </c>
+      <c r="U40" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="19:21">
+      <c r="S41" s="337" t="s">
+        <v>83</v>
+      </c>
+      <c r="T41" s="70">
+        <v>2031</v>
+      </c>
+      <c r="U41" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="42" spans="19:21">
+      <c r="S42" s="337" t="s">
+        <v>84</v>
+      </c>
+      <c r="T42" s="70">
+        <v>2032</v>
+      </c>
+      <c r="U42" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="19:21" ht="15.75" thickBot="1">
+      <c r="S43" s="339" t="s">
+        <v>85</v>
+      </c>
+      <c r="T43" s="340">
+        <v>2033</v>
+      </c>
+      <c r="U43" s="341">
+        <f>192 + 10</f>
+        <v>202</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B13:K20" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="B14:L19">
-    <cfRule type="expression" dxfId="26" priority="2">
+    <cfRule type="expression" dxfId="52" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F19 L14:L19">
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="50" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="49" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:J19">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4749,7 +5140,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59760F-A41D-4F61-BA2B-13AF059236FC}">
   <dimension ref="B1:P52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -4764,13 +5155,14 @@
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.140625" customWidth="1"/>
-    <col min="21" max="21" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:12" ht="18" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -4783,29 +5175,33 @@
       <c r="E2" s="18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K2" cm="1">
+        <f t="array" aca="1" ref="K2" ca="1">INT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"))</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3">
-        <f ca="1">160+C4</f>
-        <v>168.5</v>
+        <f ca="1">IF(K2 &lt;= O43, P40, IF(AND(K2 &gt;= O44, K2 &lt; O49), P44, IF(MOD(K2 - O40, 10) = 0, P49 + 80, P49)))</f>
+        <v>160</v>
       </c>
       <c r="D3" s="3">
         <f ca="1">C3-E3</f>
-        <v>168.5</v>
+        <v>160</v>
       </c>
       <c r="E3" s="1">
-        <f ca="1">C3 - C6 - SUMIF(H14:H51, "PTO", G14:G51)</f>
+        <f ca="1">SUM(C3 + C4) - C6 - SUMIF(H14:H51, "PTO", G14:G51)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="56" t="str" cm="1">
-        <f t="array" aca="1" ref="K3" ca="1">"PTO Reset: 02/12/" &amp; (RIGHT(CELL("filename",A2),LEN(CELL("filename",A2))-SEARCH("]",CELL("filename",A2)))) + 1</f>
+      <c r="K3" s="56" t="str">
+        <f ca="1">"PTO Reset: 02/12/" &amp; INT(K2) + 1</f>
         <v>PTO Reset: 02/12/2027</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -4816,24 +5212,24 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="15.75" thickBot="1">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="7">
-        <f ca="1">C3/8</f>
+        <f ca="1">SUM(C3 + C4) / 8</f>
         <v>21.0625</v>
       </c>
       <c r="D5" s="7">
-        <f ca="1">D3/8</f>
-        <v>21.0625</v>
+        <f ca="1">D3 / 8</f>
+        <v>20</v>
       </c>
       <c r="E5" s="8">
-        <f ca="1">E3/8</f>
+        <f ca="1">E3 / 8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -4841,7 +5237,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="10">
-        <f>C6-E6</f>
+        <f>C6 - E6</f>
         <v>19.999999999999993</v>
       </c>
       <c r="E6" s="11">
@@ -4849,24 +5245,24 @@
         <v>20.000000000000007</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="15.75" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="13">
-        <f>C6/8</f>
+        <f>C6 / 8</f>
         <v>5</v>
       </c>
       <c r="D7" s="13">
-        <f>D6/8</f>
+        <f>D6 / 8</f>
         <v>2.4999999999999991</v>
       </c>
       <c r="E7" s="14">
-        <f>E6/8</f>
+        <f>E6 / 8</f>
         <v>2.5000000000000009</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -4874,7 +5270,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="2">
-        <f>C8-E8</f>
+        <f>C8 - E8</f>
         <v>16</v>
       </c>
       <c r="E8" s="1">
@@ -4883,24 +5279,24 @@
       </c>
       <c r="K8" s="51"/>
     </row>
-    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="7">
-        <f>C8/8</f>
+        <f>C8 / 8</f>
         <v>2</v>
       </c>
       <c r="D9" s="7">
-        <f>D8/8</f>
+        <f>D8 / 8</f>
         <v>2</v>
       </c>
       <c r="E9" s="15">
-        <f>E8/8</f>
+        <f>E8 / 8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -4908,7 +5304,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="128">
-        <f>C10-E10</f>
+        <f>C10 - E10</f>
         <v>0</v>
       </c>
       <c r="E10" s="129">
@@ -4917,26 +5313,26 @@
       </c>
       <c r="K10" s="36"/>
     </row>
-    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" ht="15.75" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="131">
-        <f>C10/8</f>
+        <f>C10 / 8</f>
         <v>0.5</v>
       </c>
       <c r="D11" s="131">
-        <f>D10/8</f>
+        <f>D10 / 8</f>
         <v>0</v>
       </c>
       <c r="E11" s="132">
-        <f>E10/8</f>
+        <f>E10 / 8</f>
         <v>0.5</v>
       </c>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:12" ht="35.25" thickBot="1">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -4971,7 +5367,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12">
       <c r="B14" s="122">
         <v>46059</v>
       </c>
@@ -5010,7 +5406,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" ht="15.75" thickBot="1">
       <c r="B15" s="306">
         <v>46080</v>
       </c>
@@ -5049,7 +5445,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" ht="15.75" thickBot="1">
       <c r="B16" s="282">
         <v>46093</v>
       </c>
@@ -5088,7 +5484,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12">
       <c r="B17" s="289">
         <v>46150</v>
       </c>
@@ -5127,7 +5523,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12">
       <c r="B18" s="270">
         <v>46164</v>
       </c>
@@ -5166,7 +5562,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" ht="15.75" thickBot="1">
       <c r="B19" s="113">
         <v>46168</v>
       </c>
@@ -5205,7 +5601,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="30.75" thickBot="1">
       <c r="B20" s="103">
         <v>46196</v>
       </c>
@@ -5244,7 +5640,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="30.75" thickBot="1">
       <c r="B21" s="282">
         <v>46196</v>
       </c>
@@ -5283,7 +5679,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12">
       <c r="B22" s="279">
         <v>46226</v>
       </c>
@@ -5322,7 +5718,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12">
       <c r="B23" s="331">
         <v>46227</v>
       </c>
@@ -5361,7 +5757,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12">
       <c r="B24" s="140">
         <v>46232</v>
       </c>
@@ -5400,7 +5796,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12">
       <c r="B25" s="140">
         <v>46233</v>
       </c>
@@ -5439,7 +5835,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" ht="15.75" thickBot="1">
       <c r="B26" s="324">
         <v>46234</v>
       </c>
@@ -5478,7 +5874,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12">
       <c r="B27" s="123">
         <v>46240</v>
       </c>
@@ -5517,7 +5913,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12">
       <c r="B28" s="249">
         <v>46241</v>
       </c>
@@ -5556,7 +5952,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12">
       <c r="B29" s="249">
         <v>46244</v>
       </c>
@@ -5595,7 +5991,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12">
       <c r="B30" s="249">
         <v>46245</v>
       </c>
@@ -5634,7 +6030,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="30">
       <c r="B31" s="249">
         <v>46246</v>
       </c>
@@ -5673,7 +6069,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="30">
       <c r="B32" s="249">
         <v>46246</v>
       </c>
@@ -5712,7 +6108,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16">
       <c r="B33" s="250">
         <v>46247</v>
       </c>
@@ -5751,7 +6147,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16">
       <c r="B34" s="250">
         <v>46248</v>
       </c>
@@ -5790,7 +6186,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" ht="15.75" thickBot="1">
       <c r="B35" s="250">
         <v>46253</v>
       </c>
@@ -5829,7 +6225,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16">
       <c r="B36" s="105">
         <v>46269</v>
       </c>
@@ -5868,7 +6264,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16">
       <c r="B37" s="316">
         <v>46275</v>
       </c>
@@ -5906,17 +6302,8 @@
         <f t="shared" ca="1" si="12"/>
         <v>Passed</v>
       </c>
-      <c r="N37" s="336" t="s">
-        <v>74</v>
-      </c>
-      <c r="O37" s="98" t="s">
-        <v>75</v>
-      </c>
-      <c r="P37" s="200" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:16" ht="15.75" thickBot="1">
       <c r="B38" s="107">
         <v>46275</v>
       </c>
@@ -5954,17 +6341,8 @@
         <f t="shared" ca="1" si="12"/>
         <v>Passed</v>
       </c>
-      <c r="N38" s="342" t="s">
-        <v>76</v>
-      </c>
-      <c r="O38" s="343">
-        <v>2024</v>
-      </c>
-      <c r="P38" s="344">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="2:16" ht="15.75" thickBot="1">
       <c r="B39" s="106">
         <v>46275</v>
       </c>
@@ -6002,11 +6380,17 @@
         <f t="shared" ref="L39:L43" ca="1" si="16">IF(C39 = "TBD", "TBD", IF(B39 = "", "IDK!!", IF(TODAY() &gt; B39, "Passed", IF(TODAY() = B39, "Today!!", "Upcoming"))))</f>
         <v>Passed</v>
       </c>
-      <c r="N39" s="345"/>
-      <c r="O39" s="346"/>
-      <c r="P39" s="347"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N39" s="336" t="s">
+        <v>74</v>
+      </c>
+      <c r="O39" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="P39" s="200" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16">
       <c r="B40" s="316">
         <v>46289</v>
       </c>
@@ -6035,20 +6419,26 @@
         <v>20</v>
       </c>
       <c r="J40" s="321" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K40" s="322" t="s">
         <v>95</v>
       </c>
       <c r="L40" s="67" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Today!!</v>
-      </c>
-      <c r="N40" s="345"/>
-      <c r="O40" s="346"/>
-      <c r="P40" s="347"/>
-    </row>
-    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>Passed</v>
+      </c>
+      <c r="N40" s="342" t="s">
+        <v>76</v>
+      </c>
+      <c r="O40" s="343">
+        <v>2024</v>
+      </c>
+      <c r="P40" s="344">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" ht="15.75" thickBot="1">
       <c r="B41" s="107">
         <v>46289</v>
       </c>
@@ -6077,20 +6467,26 @@
         <v>20</v>
       </c>
       <c r="J41" s="202" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K41" s="212" t="s">
         <v>96</v>
       </c>
       <c r="L41" s="251" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Today!!</v>
-      </c>
-      <c r="N41" s="345"/>
-      <c r="O41" s="346"/>
-      <c r="P41" s="347"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+        <v>Passed</v>
+      </c>
+      <c r="N41" s="345" t="s">
+        <v>77</v>
+      </c>
+      <c r="O41" s="346">
+        <v>2025</v>
+      </c>
+      <c r="P41" s="347">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16">
       <c r="B42" s="295">
         <v>46297</v>
       </c>
@@ -6119,20 +6515,26 @@
         <v>20</v>
       </c>
       <c r="J42" s="196" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K42" s="362" t="s">
         <v>94</v>
       </c>
       <c r="L42" s="42" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="N42" s="345"/>
-      <c r="O42" s="346"/>
-      <c r="P42" s="347"/>
-    </row>
-    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>Passed</v>
+      </c>
+      <c r="N42" s="337" t="s">
+        <v>78</v>
+      </c>
+      <c r="O42" s="70">
+        <v>2026</v>
+      </c>
+      <c r="P42" s="338">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" ht="15.75" thickBot="1">
       <c r="B43" s="363">
         <v>46297</v>
       </c>
@@ -6161,20 +6563,26 @@
         <v>20</v>
       </c>
       <c r="J43" s="244" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K43" s="368" t="s">
         <v>94</v>
       </c>
       <c r="L43" s="60" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Upcoming</v>
-      </c>
-      <c r="N43" s="345"/>
-      <c r="O43" s="346"/>
-      <c r="P43" s="347"/>
-    </row>
-    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>Passed</v>
+      </c>
+      <c r="N43" s="337" t="s">
+        <v>79</v>
+      </c>
+      <c r="O43" s="70">
+        <v>2027</v>
+      </c>
+      <c r="P43" s="338">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" ht="15.75" thickBot="1">
       <c r="B44" s="124">
         <v>46353</v>
       </c>
@@ -6212,18 +6620,17 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N44" s="345" t="s">
-        <v>77</v>
-      </c>
-      <c r="O44" s="346">
-        <f>O38+1</f>
-        <v>2025</v>
-      </c>
-      <c r="P44" s="347">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N44" s="337" t="s">
+        <v>80</v>
+      </c>
+      <c r="O44" s="70">
+        <v>2028</v>
+      </c>
+      <c r="P44" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16">
       <c r="B45" s="112">
         <v>46380</v>
       </c>
@@ -6262,17 +6669,16 @@
         <v>Upcoming</v>
       </c>
       <c r="N45" s="337" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O45" s="70">
-        <f>O44+1</f>
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="P45" s="338">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16">
       <c r="B46" s="120">
         <v>46384</v>
       </c>
@@ -6311,17 +6717,16 @@
         <v>Upcoming</v>
       </c>
       <c r="N46" s="337" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O46" s="70">
-        <f t="shared" ref="O46:O52" si="17">O45+1</f>
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="P46" s="338">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16">
       <c r="B47" s="270">
         <v>46385</v>
       </c>
@@ -6336,7 +6741,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F47" s="276">
-        <f t="shared" ref="F47:F49" si="18">((E47 - D47) * 24)</f>
+        <f t="shared" ref="F47:F49" si="17">((E47 - D47) * 24)</f>
         <v>8.9999999999999982</v>
       </c>
       <c r="G47" s="274">
@@ -6360,17 +6765,16 @@
         <v>Upcoming</v>
       </c>
       <c r="N47" s="337" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O47" s="70">
-        <f t="shared" si="17"/>
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="P47" s="338">
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16">
       <c r="B48" s="270">
         <v>46386</v>
       </c>
@@ -6385,7 +6789,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F48" s="276">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G48" s="274">
@@ -6409,17 +6813,16 @@
         <v>Upcoming</v>
       </c>
       <c r="N48" s="337" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O48" s="70">
-        <f t="shared" si="17"/>
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="P48" s="338">
         <v>176</v>
       </c>
     </row>
-    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" ht="15.75" thickBot="1">
       <c r="B49" s="113">
         <v>46387</v>
       </c>
@@ -6434,7 +6837,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F49" s="276">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="G49" s="274">
@@ -6457,31 +6860,31 @@
         <f t="shared" ca="1" si="8"/>
         <v>Upcoming</v>
       </c>
-      <c r="N49" s="337" t="s">
-        <v>82</v>
-      </c>
-      <c r="O49" s="70">
-        <f t="shared" si="17"/>
-        <v>2030</v>
-      </c>
-      <c r="P49" s="338">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N49" s="339" t="s">
+        <v>85</v>
+      </c>
+      <c r="O49" s="340">
+        <v>2033</v>
+      </c>
+      <c r="P49" s="341">
+        <f>192 + 10</f>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16">
       <c r="B50" s="102"/>
       <c r="C50" s="165" t="str">
-        <f t="shared" ref="C50:C51" si="19">IF(ISNUMBER(FIND("?", B50, 1)), "TBD", TEXT(B50, "ddd"))</f>
+        <f t="shared" ref="C50:C51" si="18">IF(ISNUMBER(FIND("?", B50, 1)), "TBD", TEXT(B50, "ddd"))</f>
         <v>Sat</v>
       </c>
       <c r="D50" s="157"/>
       <c r="E50" s="157"/>
       <c r="F50" s="220">
-        <f t="shared" ref="F50:F51" si="20">((E50 - D50) * 24)</f>
+        <f t="shared" ref="F50:F51" si="19">((E50 - D50) * 24)</f>
         <v>0</v>
       </c>
       <c r="G50" s="217">
-        <f t="shared" ref="G50:G51" si="21">IF(F50 &gt; 4, (F50 - 1), F50)</f>
+        <f t="shared" ref="G50:G51" si="20">IF(F50 &gt; 4, (F50 - 1), F50)</f>
         <v>0</v>
       </c>
       <c r="H50" s="180"/>
@@ -6493,34 +6896,24 @@
       </c>
       <c r="K50" s="205"/>
       <c r="L50" s="252" t="str">
-        <f t="shared" ref="L50:L51" ca="1" si="22">IF(C50 = "TBD", "TBD", IF(B50 = "", "IDK!!", IF(TODAY() &gt; B50, "Passed", IF(TODAY() = B50, "Today!!", "Upcoming"))))</f>
+        <f t="shared" ref="L50:L51" ca="1" si="21">IF(C50 = "TBD", "TBD", IF(B50 = "", "IDK!!", IF(TODAY() &gt; B50, "Passed", IF(TODAY() = B50, "Today!!", "Upcoming"))))</f>
         <v>IDK!!</v>
       </c>
-      <c r="N50" s="337" t="s">
-        <v>83</v>
-      </c>
-      <c r="O50" s="70">
-        <f t="shared" si="17"/>
-        <v>2031</v>
-      </c>
-      <c r="P50" s="338">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="2:16" ht="15.75" thickBot="1">
       <c r="B51" s="259"/>
       <c r="C51" s="253" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>Sat</v>
       </c>
       <c r="D51" s="260"/>
       <c r="E51" s="260"/>
       <c r="F51" s="261">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="253">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="253">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H51" s="254"/>
@@ -6532,21 +6925,11 @@
       </c>
       <c r="K51" s="255"/>
       <c r="L51" s="251" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="21"/>
         <v>IDK!!</v>
       </c>
-      <c r="N51" s="337" t="s">
-        <v>84</v>
-      </c>
-      <c r="O51" s="70">
-        <f t="shared" si="17"/>
-        <v>2032</v>
-      </c>
-      <c r="P51" s="338">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="2:16" ht="15.75" thickBot="1">
       <c r="B52" s="86" t="s">
         <v>11</v>
       </c>
@@ -6566,47 +6949,41 @@
       <c r="J52" s="302"/>
       <c r="K52" s="302"/>
       <c r="L52" s="302"/>
-      <c r="N52" s="339" t="s">
-        <v>85</v>
-      </c>
-      <c r="O52" s="340">
-        <f t="shared" si="17"/>
-        <v>2033</v>
-      </c>
-      <c r="P52" s="341">
-        <f>192 + 10</f>
-        <v>202</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="B13:K52" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B14:L51">
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F51 L14:L51">
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="18" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="I14:J51">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3 E5 E8:E9">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="E3 E5 E8:E9">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J51">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"N/A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
-      <formula>"No"</formula>
+  <conditionalFormatting sqref="E3 E5 E8:E9">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6618,7 +6995,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD57EB3B-515A-4E94-895F-88D262D477C2}">
   <dimension ref="B1:H44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -6628,8 +7005,8 @@
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:8" ht="18" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -6643,7 +7020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -6664,7 +7041,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -6675,7 +7052,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="15.75" thickBot="1">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -6692,7 +7069,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -6708,7 +7085,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="15.75" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -6725,7 +7102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -6742,7 +7119,7 @@
       </c>
       <c r="G8" s="51"/>
     </row>
-    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="15.75" thickBot="1">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -6759,7 +7136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -6776,7 +7153,7 @@
       </c>
       <c r="G10" s="36"/>
     </row>
-    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="15.75" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -6794,8 +7171,8 @@
       </c>
       <c r="G11" s="36"/>
     </row>
-    <row r="12" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:8" ht="35.25" thickBot="1">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -6818,7 +7195,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="15.75" thickBot="1">
       <c r="B14" s="133">
         <v>45743</v>
       </c>
@@ -6843,7 +7220,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8">
       <c r="B15" s="102">
         <v>45783</v>
       </c>
@@ -6868,7 +7245,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8">
       <c r="B16" s="140">
         <v>45797</v>
       </c>
@@ -6893,7 +7270,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="15.75" thickBot="1">
       <c r="B17" s="137">
         <v>45800</v>
       </c>
@@ -6918,7 +7295,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" ht="15.75" thickBot="1">
       <c r="B18" s="148">
         <v>45827</v>
       </c>
@@ -6943,7 +7320,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" ht="15.75" thickBot="1">
       <c r="B19" s="143">
         <v>45849</v>
       </c>
@@ -6968,7 +7345,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8">
       <c r="B20" s="105">
         <v>45873</v>
       </c>
@@ -6993,7 +7370,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8">
       <c r="B21" s="106">
         <v>45874</v>
       </c>
@@ -7018,7 +7395,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8">
       <c r="B22" s="106">
         <v>45875</v>
       </c>
@@ -7043,7 +7420,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8">
       <c r="B23" s="106">
         <v>45876</v>
       </c>
@@ -7068,7 +7445,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8">
       <c r="B24" s="106">
         <v>45877</v>
       </c>
@@ -7093,7 +7470,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8">
       <c r="B25" s="106">
         <v>45880</v>
       </c>
@@ -7118,7 +7495,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8">
       <c r="B26" s="106">
         <v>45880</v>
       </c>
@@ -7143,7 +7520,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8">
       <c r="B27" s="106">
         <v>45881</v>
       </c>
@@ -7168,7 +7545,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8">
       <c r="B28" s="106">
         <v>45882</v>
       </c>
@@ -7193,7 +7570,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8">
       <c r="B29" s="106">
         <v>45883</v>
       </c>
@@ -7218,7 +7595,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8">
       <c r="B30" s="107">
         <v>45884</v>
       </c>
@@ -7243,7 +7620,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8">
       <c r="B31" s="107">
         <v>45884</v>
       </c>
@@ -7268,7 +7645,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8">
       <c r="B32" s="107">
         <v>45884</v>
       </c>
@@ -7293,7 +7670,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8">
       <c r="B33" s="107">
         <v>45889</v>
       </c>
@@ -7318,7 +7695,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8" ht="15.75" thickBot="1">
       <c r="B34" s="107">
         <v>45898</v>
       </c>
@@ -7343,7 +7720,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" ht="15.75" thickBot="1">
       <c r="B35" s="124">
         <v>45908</v>
       </c>
@@ -7368,7 +7745,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" ht="15.75" thickBot="1">
       <c r="B36" s="108">
         <v>45989</v>
       </c>
@@ -7393,7 +7770,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8">
       <c r="B37" s="109">
         <v>46014</v>
       </c>
@@ -7418,7 +7795,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8">
       <c r="B38" s="110">
         <v>46015</v>
       </c>
@@ -7443,7 +7820,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8">
       <c r="B39" s="110">
         <v>46017</v>
       </c>
@@ -7468,7 +7845,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8">
       <c r="B40" s="111">
         <v>46020</v>
       </c>
@@ -7493,7 +7870,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8">
       <c r="B41" s="111">
         <v>46021</v>
       </c>
@@ -7518,7 +7895,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" ht="15.75" thickBot="1">
       <c r="B42" s="111">
         <v>46022</v>
       </c>
@@ -7543,7 +7920,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" ht="15.75" thickBot="1">
       <c r="B43" s="124">
         <v>46024</v>
       </c>
@@ -7568,7 +7945,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:8" ht="15.75" thickBot="1">
       <c r="B44" s="6" t="s">
         <v>11</v>
       </c>
@@ -7585,22 +7962,22 @@
   </sheetData>
   <autoFilter ref="B13:G44" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="C14:C43 H14:H43">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="44" priority="9" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F43">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="8" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7613,7 +7990,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D12B9BF-3416-48A7-87E4-2977D80A472D}">
   <dimension ref="B1:K48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
@@ -7626,8 +8003,8 @@
     <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:11" ht="18" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -7641,7 +8018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -7662,7 +8039,7 @@
         <v>PTO Reset: 02/12/2026</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -7673,7 +8050,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" ht="15.75" thickBot="1">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -7690,7 +8067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -7706,7 +8083,7 @@
         <v>8.5000000000000071</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" ht="15.75" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -7723,7 +8100,7 @@
         <v>1.0625000000000009</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -7740,7 +8117,7 @@
       </c>
       <c r="J8" s="51"/>
     </row>
-    <row r="9" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="15.75" thickBot="1">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -7757,7 +8134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -7774,7 +8151,7 @@
       </c>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="15.75" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -7792,8 +8169,8 @@
       </c>
       <c r="J11" s="36"/>
     </row>
-    <row r="12" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:11" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:11" ht="35.25" thickBot="1">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -7825,7 +8202,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" ht="15.75" thickBot="1">
       <c r="B14" s="133">
         <v>45743</v>
       </c>
@@ -7861,7 +8238,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11">
       <c r="B15" s="102">
         <v>45783</v>
       </c>
@@ -7897,7 +8274,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11">
       <c r="B16" s="140">
         <v>45797</v>
       </c>
@@ -7933,7 +8310,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" ht="15.75" thickBot="1">
       <c r="B17" s="137">
         <v>45800</v>
       </c>
@@ -7969,7 +8346,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" ht="15.75" thickBot="1">
       <c r="B18" s="148">
         <v>45827</v>
       </c>
@@ -8005,7 +8382,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="15.75" thickBot="1">
       <c r="B19" s="143">
         <v>45849</v>
       </c>
@@ -8041,7 +8418,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11">
       <c r="B20" s="105">
         <v>45873</v>
       </c>
@@ -8077,7 +8454,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11">
       <c r="B21" s="106">
         <v>45874</v>
       </c>
@@ -8113,7 +8490,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11">
       <c r="B22" s="106">
         <v>45875</v>
       </c>
@@ -8149,7 +8526,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11">
       <c r="B23" s="106">
         <v>45876</v>
       </c>
@@ -8185,7 +8562,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11">
       <c r="B24" s="106">
         <v>45877</v>
       </c>
@@ -8221,7 +8598,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11">
       <c r="B25" s="106">
         <v>45880</v>
       </c>
@@ -8257,7 +8634,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11">
       <c r="B26" s="106">
         <v>45880</v>
       </c>
@@ -8293,7 +8670,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11">
       <c r="B27" s="106">
         <v>45881</v>
       </c>
@@ -8329,7 +8706,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11">
       <c r="B28" s="106">
         <v>45882</v>
       </c>
@@ -8365,7 +8742,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11">
       <c r="B29" s="106">
         <v>45883</v>
       </c>
@@ -8401,7 +8778,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11">
       <c r="B30" s="107">
         <v>45884</v>
       </c>
@@ -8437,7 +8814,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11">
       <c r="B31" s="107">
         <v>45884</v>
       </c>
@@ -8473,7 +8850,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11">
       <c r="B32" s="107">
         <v>45884</v>
       </c>
@@ -8509,7 +8886,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11">
       <c r="B33" s="107">
         <v>45889</v>
       </c>
@@ -8545,7 +8922,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1">
       <c r="B34" s="107">
         <v>45898</v>
       </c>
@@ -8581,7 +8958,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" ht="15.75" thickBot="1">
       <c r="B35" s="148">
         <v>45908</v>
       </c>
@@ -8617,7 +8994,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11">
       <c r="B36" s="229">
         <v>45933</v>
       </c>
@@ -8653,7 +9030,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" ht="15.75" thickBot="1">
       <c r="B37" s="282">
         <v>45936</v>
       </c>
@@ -8689,7 +9066,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" ht="15.75" thickBot="1">
       <c r="B38" s="289">
         <v>45989</v>
       </c>
@@ -8725,7 +9102,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11">
       <c r="B39" s="295">
         <v>45999</v>
       </c>
@@ -8761,7 +9138,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11">
       <c r="B40" s="234">
         <v>46006</v>
       </c>
@@ -8797,7 +9174,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11">
       <c r="B41" s="234">
         <v>46014</v>
       </c>
@@ -8833,7 +9210,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11">
       <c r="B42" s="234">
         <v>46015</v>
       </c>
@@ -8869,7 +9246,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11">
       <c r="B43" s="110">
         <v>46017</v>
       </c>
@@ -8905,7 +9282,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11">
       <c r="B44" s="111">
         <v>46020</v>
       </c>
@@ -8941,7 +9318,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11">
       <c r="B45" s="111">
         <v>46021</v>
       </c>
@@ -8977,7 +9354,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="46" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" ht="15.75" thickBot="1">
       <c r="B46" s="111">
         <v>46022</v>
       </c>
@@ -9013,7 +9390,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="47" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" ht="15.75" thickBot="1">
       <c r="B47" s="124">
         <v>46024</v>
       </c>
@@ -9049,7 +9426,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="48" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11" ht="15.75" thickBot="1">
       <c r="B48" s="6" t="s">
         <v>11</v>
       </c>
@@ -9072,27 +9449,27 @@
   </sheetData>
   <autoFilter ref="B13:J48" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="B14:K47">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F47 K14:K47">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="39" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I47">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9106,7 +9483,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25002DC1-579B-4118-A464-8DA972BBC903}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:G43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
@@ -9117,8 +9494,8 @@
     <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:7" ht="18" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -9136,7 +9513,7 @@
         <v>PTO Reset: 02/12/2025</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -9152,7 +9529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="15.75" thickBot="1">
       <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
@@ -9169,7 +9546,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7">
       <c r="B5" s="9" t="s">
         <v>15</v>
       </c>
@@ -9186,7 +9563,7 @@
       </c>
       <c r="G5" s="55"/>
     </row>
-    <row r="6" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="15.75" thickBot="1">
       <c r="B6" s="12" t="s">
         <v>16</v>
       </c>
@@ -9204,7 +9581,7 @@
       </c>
       <c r="G6" s="36"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7">
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
@@ -9220,7 +9597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="15.75" thickBot="1">
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
@@ -9238,7 +9615,7 @@
       </c>
       <c r="G8" s="36"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7">
       <c r="B9" s="127" t="s">
         <v>22</v>
       </c>
@@ -9255,7 +9632,7 @@
       </c>
       <c r="G9" s="36"/>
     </row>
-    <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="15.75" thickBot="1">
       <c r="B10" s="130" t="s">
         <v>23</v>
       </c>
@@ -9273,8 +9650,8 @@
       </c>
       <c r="G10" s="36"/>
     </row>
-    <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="2:7" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="12" spans="2:7" ht="35.25" thickBot="1">
       <c r="B12" s="28" t="s">
         <v>1</v>
       </c>
@@ -9294,7 +9671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="30">
       <c r="B13" s="112">
         <v>45436</v>
       </c>
@@ -9315,7 +9692,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="15.75" thickBot="1">
       <c r="B14" s="113">
         <v>45443</v>
       </c>
@@ -9336,7 +9713,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="15.75" thickBot="1">
       <c r="B15" s="114">
         <v>45499</v>
       </c>
@@ -9357,7 +9734,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7">
       <c r="B16" s="115">
         <v>45509</v>
       </c>
@@ -9378,7 +9755,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7">
       <c r="B17" s="116">
         <v>45510</v>
       </c>
@@ -9399,7 +9776,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7">
       <c r="B18" s="116">
         <v>45511</v>
       </c>
@@ -9420,7 +9797,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7">
       <c r="B19" s="116">
         <v>45512</v>
       </c>
@@ -9441,7 +9818,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7">
       <c r="B20" s="116">
         <v>45513</v>
       </c>
@@ -9462,7 +9839,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7">
       <c r="B21" s="117">
         <v>45516</v>
       </c>
@@ -9483,7 +9860,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7">
       <c r="B22" s="117">
         <v>45517</v>
       </c>
@@ -9504,7 +9881,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7">
       <c r="B23" s="117">
         <v>45518</v>
       </c>
@@ -9525,7 +9902,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7">
       <c r="B24" s="117">
         <v>45519</v>
       </c>
@@ -9546,7 +9923,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7">
       <c r="B25" s="118">
         <v>45520</v>
       </c>
@@ -9567,7 +9944,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7">
       <c r="B26" s="116">
         <v>45525</v>
       </c>
@@ -9588,7 +9965,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7">
       <c r="B27" s="116">
         <v>45530</v>
       </c>
@@ -9609,7 +9986,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="15.75" thickBot="1">
       <c r="B28" s="119">
         <v>45534</v>
       </c>
@@ -9630,7 +10007,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7">
       <c r="B29" s="112">
         <v>45567</v>
       </c>
@@ -9651,7 +10028,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7">
       <c r="B30" s="120">
         <v>45573</v>
       </c>
@@ -9672,7 +10049,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7">
       <c r="B31" s="121">
         <v>45579</v>
       </c>
@@ -9693,7 +10070,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="15.75" thickBot="1">
       <c r="B32" s="113">
         <v>45580</v>
       </c>
@@ -9714,7 +10091,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7">
       <c r="B33" s="103">
         <v>45597</v>
       </c>
@@ -9735,7 +10112,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="15.75" thickBot="1">
       <c r="B34" s="104">
         <v>45625</v>
       </c>
@@ -9756,7 +10133,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7">
       <c r="B35" s="122">
         <v>45653</v>
       </c>
@@ -9777,7 +10154,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7">
       <c r="B36" s="123">
         <v>45656</v>
       </c>
@@ -9798,7 +10175,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7">
       <c r="B37" s="123">
         <v>45657</v>
       </c>
@@ -9819,7 +10196,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7">
       <c r="B38" s="123">
         <v>45659</v>
       </c>
@@ -9840,7 +10217,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7">
       <c r="B39" s="123">
         <v>45660</v>
       </c>
@@ -9861,7 +10238,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7">
       <c r="B40" s="123">
         <v>45663</v>
       </c>
@@ -9882,7 +10259,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7">
       <c r="B41" s="123">
         <v>45664</v>
       </c>
@@ -9903,7 +10280,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="15.75" thickBot="1">
       <c r="B42" s="114">
         <v>45665</v>
       </c>
@@ -9924,7 +10301,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="15.75" thickBot="1">
       <c r="B43" s="86" t="s">
         <v>11</v>
       </c>
@@ -9940,17 +10317,17 @@
   </sheetData>
   <autoFilter ref="B12:G43" xr:uid="{25002DC1-579B-4118-A464-8DA972BBC903}"/>
   <conditionalFormatting sqref="E3:E4">
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E10">
-    <cfRule type="cellIs" dxfId="4" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="36" priority="15" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E42">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9976,7 +10353,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8D74E6-E2F4-497A-863D-7746D04C8BB1}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:G22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -9986,8 +10363,8 @@
     <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:7" ht="18" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>17</v>
       </c>
@@ -10001,7 +10378,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
@@ -10022,7 +10399,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>38</v>
       </c>
@@ -10033,7 +10410,7 @@
       <c r="D4" s="74"/>
       <c r="E4" s="75"/>
     </row>
-    <row r="5" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="15.75" thickBot="1">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -10050,7 +10427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7">
       <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
@@ -10066,7 +10443,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="15.75" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
@@ -10083,7 +10460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -10100,7 +10477,7 @@
       </c>
       <c r="G8" s="51"/>
     </row>
-    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="15.75" thickBot="1">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -10117,7 +10494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7">
       <c r="B10" s="127" t="s">
         <v>22</v>
       </c>
@@ -10134,7 +10511,7 @@
       </c>
       <c r="G10" s="36"/>
     </row>
-    <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="15.75" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>23</v>
       </c>
@@ -10152,8 +10529,8 @@
       </c>
       <c r="G11" s="36"/>
     </row>
-    <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:7" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:7" ht="35.25" thickBot="1">
       <c r="B13" s="28" t="s">
         <v>1</v>
       </c>
@@ -10173,7 +10550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7">
       <c r="B14" s="38">
         <v>45658</v>
       </c>
@@ -10190,7 +10567,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="15.75" thickBot="1">
       <c r="B15" s="31">
         <v>45658</v>
       </c>
@@ -10207,7 +10584,7 @@
         <v>Passed</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="15.75" thickBot="1">
       <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
@@ -10220,22 +10597,22 @@
       <c r="F16" s="27"/>
       <c r="G16" s="20"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2">
       <c r="B21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
         <v>33</v>
       </c>
@@ -10243,17 +10620,17 @@
   </sheetData>
   <autoFilter ref="B13:G13" xr:uid="{3C8D74E6-E2F4-497A-863D-7746D04C8BB1}"/>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="33" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E15">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988B413E-B41A-4CBE-86BC-C17C4497378D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05F22F8-5319-4325-9BD1-A200306C2451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="105" windowWidth="33285" windowHeight="20625" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="38655" yWindow="0" windowWidth="30435" windowHeight="21705" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="97">
   <si>
     <t>Total</t>
   </si>
@@ -2567,316 +2567,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <font>
         <b/>
@@ -3056,6 +2747,75 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3205,7 +2965,7 @@
       <xdr:col>27</xdr:col>
       <xdr:colOff>178174</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>173692</xdr:rowOff>
+      <xdr:rowOff>151280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4523,7 +4283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2671213-B148-403C-9F48-0EB30902282E}">
-  <dimension ref="B1:W43"/>
+  <dimension ref="B1:W50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -4570,7 +4330,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3">
-        <f>160</f>
+        <f ca="1">IF(K2 &lt;= O44, P41, IF(AND(K2 &gt;= O45, K2 &lt; O50), P45, IF(MOD(K2 - O41, 10) = 0, P50 + 80, P50)))</f>
         <v>160</v>
       </c>
       <c r="D3" s="3">
@@ -4979,7 +4739,7 @@
       <c r="L20" s="302"/>
     </row>
     <row r="32" spans="2:23" ht="15.75" thickBot="1"/>
-    <row r="33" spans="19:21" ht="15.75" thickBot="1">
+    <row r="33" spans="14:21" ht="15.75" thickBot="1">
       <c r="S33" s="336" t="s">
         <v>74</v>
       </c>
@@ -4990,7 +4750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="19:21">
+    <row r="34" spans="14:21">
       <c r="S34" s="342" t="s">
         <v>76</v>
       </c>
@@ -5001,7 +4761,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="19:21">
+    <row r="35" spans="14:21">
       <c r="S35" s="345" t="s">
         <v>77</v>
       </c>
@@ -5012,7 +4772,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="19:21">
+    <row r="36" spans="14:21">
       <c r="S36" s="337" t="s">
         <v>78</v>
       </c>
@@ -5023,7 +4783,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="19:21">
+    <row r="37" spans="14:21">
       <c r="S37" s="337" t="s">
         <v>79</v>
       </c>
@@ -5034,7 +4794,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="38" spans="19:21">
+    <row r="38" spans="14:21">
       <c r="S38" s="337" t="s">
         <v>80</v>
       </c>
@@ -5045,7 +4805,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="19:21">
+    <row r="39" spans="14:21" ht="15.75" thickBot="1">
       <c r="S39" s="337" t="s">
         <v>81</v>
       </c>
@@ -5056,7 +4816,16 @@
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="19:21">
+    <row r="40" spans="14:21" ht="15.75" thickBot="1">
+      <c r="N40" s="336" t="s">
+        <v>74</v>
+      </c>
+      <c r="O40" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="P40" s="200" t="s">
+        <v>2</v>
+      </c>
       <c r="S40" s="337" t="s">
         <v>82</v>
       </c>
@@ -5067,7 +4836,16 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="19:21">
+    <row r="41" spans="14:21">
+      <c r="N41" s="342" t="s">
+        <v>76</v>
+      </c>
+      <c r="O41" s="343">
+        <v>2024</v>
+      </c>
+      <c r="P41" s="344">
+        <v>160</v>
+      </c>
       <c r="S41" s="337" t="s">
         <v>83</v>
       </c>
@@ -5078,7 +4856,16 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="19:21">
+    <row r="42" spans="14:21">
+      <c r="N42" s="345" t="s">
+        <v>77</v>
+      </c>
+      <c r="O42" s="346">
+        <v>2025</v>
+      </c>
+      <c r="P42" s="347">
+        <v>160</v>
+      </c>
       <c r="S42" s="337" t="s">
         <v>84</v>
       </c>
@@ -5089,7 +4876,16 @@
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="19:21" ht="15.75" thickBot="1">
+    <row r="43" spans="14:21" ht="15.75" thickBot="1">
+      <c r="N43" s="337" t="s">
+        <v>78</v>
+      </c>
+      <c r="O43" s="70">
+        <v>2026</v>
+      </c>
+      <c r="P43" s="338">
+        <v>160</v>
+      </c>
       <c r="S43" s="339" t="s">
         <v>85</v>
       </c>
@@ -5101,33 +4897,111 @@
         <v>202</v>
       </c>
     </row>
+    <row r="44" spans="14:21">
+      <c r="N44" s="337" t="s">
+        <v>79</v>
+      </c>
+      <c r="O44" s="70">
+        <v>2027</v>
+      </c>
+      <c r="P44" s="338">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="14:21">
+      <c r="N45" s="337" t="s">
+        <v>80</v>
+      </c>
+      <c r="O45" s="70">
+        <v>2028</v>
+      </c>
+      <c r="P45" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="14:21">
+      <c r="N46" s="337" t="s">
+        <v>81</v>
+      </c>
+      <c r="O46" s="70">
+        <v>2029</v>
+      </c>
+      <c r="P46" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="14:21">
+      <c r="N47" s="337" t="s">
+        <v>82</v>
+      </c>
+      <c r="O47" s="70">
+        <v>2030</v>
+      </c>
+      <c r="P47" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="14:21">
+      <c r="N48" s="337" t="s">
+        <v>83</v>
+      </c>
+      <c r="O48" s="70">
+        <v>2031</v>
+      </c>
+      <c r="P48" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="14:16">
+      <c r="N49" s="337" t="s">
+        <v>84</v>
+      </c>
+      <c r="O49" s="70">
+        <v>2032</v>
+      </c>
+      <c r="P49" s="338">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="14:16" ht="15.75" thickBot="1">
+      <c r="N50" s="339" t="s">
+        <v>85</v>
+      </c>
+      <c r="O50" s="340">
+        <v>2033</v>
+      </c>
+      <c r="P50" s="341">
+        <f>192 + 10</f>
+        <v>202</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B13:K20" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="B14:L19">
-    <cfRule type="expression" dxfId="52" priority="2">
+    <cfRule type="expression" dxfId="27" priority="2">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F19 L14:L19">
-    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="50" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="49" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:J19">
-    <cfRule type="cellIs" dxfId="48" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6954,36 +6828,32 @@
   <autoFilter ref="B13:K52" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B14:L51">
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="21" priority="6">
       <formula>$L14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F51 L14:L51">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J51">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
-      <formula>"N/A"</formula>
+  <conditionalFormatting sqref="E3 E5 E8:E9">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+      <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
-      <formula>"No"</formula>
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="lessThan">
+      <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3 E5 E8:E9">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3 E5 E8:E9">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
-      <formula>0</formula>
+  <conditionalFormatting sqref="I14:J51">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
+      <formula>"N/A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3 E5 E8:E9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>0</formula>
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7962,22 +7832,22 @@
   </sheetData>
   <autoFilter ref="B13:G44" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="C14:C43 H14:H43">
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="45" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="44" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F43">
-    <cfRule type="cellIs" dxfId="43" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9449,27 +9319,27 @@
   </sheetData>
   <autoFilter ref="B13:J48" xr:uid="{4B51B8F7-4ACE-45CA-965B-2AD2897F333A}"/>
   <conditionalFormatting sqref="B14:K47">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$K14="Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:F47 K14:K47">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="39" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I47">
-    <cfRule type="cellIs" dxfId="38" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10317,17 +10187,17 @@
   </sheetData>
   <autoFilter ref="B12:G43" xr:uid="{25002DC1-579B-4118-A464-8DA972BBC903}"/>
   <conditionalFormatting sqref="E3:E4">
-    <cfRule type="cellIs" dxfId="37" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E10">
-    <cfRule type="cellIs" dxfId="36" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="15" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E42">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10620,17 +10490,17 @@
   </sheetData>
   <autoFilter ref="B13:G13" xr:uid="{3C8D74E6-E2F4-497A-863D-7746D04C8BB1}"/>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E5:E11">
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E15">
-    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/PTO_Tracking.xlsx
+++ b/PTO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05F22F8-5319-4325-9BD1-A200306C2451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68BA7A1-0213-4E47-AC6B-2AC6EF289242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38655" yWindow="0" windowWidth="30435" windowHeight="21705" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
+    <workbookView xWindow="38520" yWindow="0" windowWidth="30435" windowHeight="21705" activeTab="1" xr2:uid="{27E0B3AA-74C4-485B-A59F-76780996FF82}"/>
   </bookViews>
   <sheets>
     <sheet name="2027" sheetId="8" r:id="rId1"/>
